--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -28639,6 +28639,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="G1230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1231" t="n">
+        <v>10803</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>1.32500004768372</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>1.32500004768372</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G1231" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -28685,6 +28685,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1232" t="n">
+        <v>10039</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G1232" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -28708,6 +28708,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1233" t="n">
+        <v>8150</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="G1233" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -28731,6 +28731,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1234" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G1234" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -28572,22 +28572,22 @@
     </row>
     <row r="1227">
       <c r="A1227" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1227" t="n">
-        <v>6113</v>
+        <v>0</v>
       </c>
       <c r="C1227" t="n">
-        <v>1.33500003814697</v>
+        <v>1.37000000476837</v>
       </c>
       <c r="D1227" t="n">
-        <v>1.30499994754791</v>
+        <v>1.37000000476837</v>
       </c>
       <c r="E1227" t="n">
-        <v>1.33500003814697</v>
+        <v>1.37000000476837</v>
       </c>
       <c r="F1227" t="n">
-        <v>1.33000004291534</v>
+        <v>1.37000000476837</v>
       </c>
       <c r="G1227" t="s">
         <v>7</v>
@@ -28595,22 +28595,22 @@
     </row>
     <row r="1228">
       <c r="A1228" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1228" t="n">
-        <v>74</v>
+        <v>6113</v>
       </c>
       <c r="C1228" t="n">
-        <v>1.29499995708466</v>
+        <v>1.33500003814697</v>
       </c>
       <c r="D1228" t="n">
-        <v>1.29499995708466</v>
+        <v>1.30499994754791</v>
       </c>
       <c r="E1228" t="n">
-        <v>1.29499995708466</v>
+        <v>1.33500003814697</v>
       </c>
       <c r="F1228" t="n">
-        <v>1.29499995708466</v>
+        <v>1.33000004291534</v>
       </c>
       <c r="G1228" t="s">
         <v>7</v>
@@ -28618,22 +28618,22 @@
     </row>
     <row r="1229">
       <c r="A1229" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1229" t="n">
-        <v>10000</v>
+        <v>74</v>
       </c>
       <c r="C1229" t="n">
-        <v>1.375</v>
+        <v>1.29499995708466</v>
       </c>
       <c r="D1229" t="n">
-        <v>1.31500005722046</v>
+        <v>1.29499995708466</v>
       </c>
       <c r="E1229" t="n">
-        <v>1.31500005722046</v>
+        <v>1.29499995708466</v>
       </c>
       <c r="F1229" t="n">
-        <v>1.36000001430511</v>
+        <v>1.29499995708466</v>
       </c>
       <c r="G1229" t="s">
         <v>7</v>
@@ -28641,19 +28641,19 @@
     </row>
     <row r="1230">
       <c r="A1230" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1230" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="C1230" t="n">
-        <v>1.36000001430511</v>
+        <v>1.375</v>
       </c>
       <c r="D1230" t="n">
-        <v>1.36000001430511</v>
+        <v>1.31500005722046</v>
       </c>
       <c r="E1230" t="n">
-        <v>1.36000001430511</v>
+        <v>1.31500005722046</v>
       </c>
       <c r="F1230" t="n">
         <v>1.36000001430511</v>
@@ -28664,22 +28664,22 @@
     </row>
     <row r="1231">
       <c r="A1231" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1231" t="n">
-        <v>10803</v>
+        <v>0</v>
       </c>
       <c r="C1231" t="n">
-        <v>1.375</v>
+        <v>1.36000001430511</v>
       </c>
       <c r="D1231" t="n">
-        <v>1.32500004768372</v>
+        <v>1.36000001430511</v>
       </c>
       <c r="E1231" t="n">
-        <v>1.32500004768372</v>
+        <v>1.36000001430511</v>
       </c>
       <c r="F1231" t="n">
-        <v>1.375</v>
+        <v>1.36000001430511</v>
       </c>
       <c r="G1231" t="s">
         <v>7</v>
@@ -28687,19 +28687,19 @@
     </row>
     <row r="1232">
       <c r="A1232" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1232" t="n">
-        <v>10039</v>
+        <v>10803</v>
       </c>
       <c r="C1232" t="n">
         <v>1.375</v>
       </c>
       <c r="D1232" t="n">
-        <v>1.3400000333786</v>
+        <v>1.32500004768372</v>
       </c>
       <c r="E1232" t="n">
-        <v>1.3400000333786</v>
+        <v>1.32500004768372</v>
       </c>
       <c r="F1232" t="n">
         <v>1.375</v>
@@ -28710,10 +28710,10 @@
     </row>
     <row r="1233">
       <c r="A1233" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1233" t="n">
-        <v>8150</v>
+        <v>10039</v>
       </c>
       <c r="C1233" t="n">
         <v>1.375</v>
@@ -28722,7 +28722,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="E1233" t="n">
-        <v>1.375</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="F1233" t="n">
         <v>1.375</v>
@@ -28733,22 +28733,22 @@
     </row>
     <row r="1234">
       <c r="A1234" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1234" t="n">
-        <v>3000</v>
+        <v>8150</v>
       </c>
       <c r="C1234" t="n">
         <v>1.375</v>
       </c>
       <c r="D1234" t="n">
-        <v>1.37000000476837</v>
+        <v>1.3400000333786</v>
       </c>
       <c r="E1234" t="n">
         <v>1.375</v>
       </c>
       <c r="F1234" t="n">
-        <v>1.37000000476837</v>
+        <v>1.375</v>
       </c>
       <c r="G1234" t="s">
         <v>7</v>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -32519,7 +32519,7 @@
         <v>20000</v>
       </c>
       <c r="C1237" t="n">
-        <v>1.38999998569489</v>
+        <v>1.39999997615814</v>
       </c>
       <c r="D1237" t="n">
         <v>1.37000000476837</v>
@@ -32534,6 +32534,32 @@
         <v>1.39999997615814</v>
       </c>
       <c r="H1237" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1238" t="n">
+        <v>39248</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>1.44500005245209</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>1.44000005722046</v>
+      </c>
+      <c r="H1238" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668828010559</v>
+        <v>2.33668804168701</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749733924866</v>
+        <v>2.22749710083008</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818855285645</v>
+        <v>2.18818831443787</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0440559387207</v>
+        <v>2.04405617713928</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486523628235</v>
+        <v>1.93486499786377</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761494636536</v>
+        <v>2.15761470794678</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176222801208</v>
+        <v>1.92176246643066</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555644989014</v>
+        <v>1.89555656909943</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026195526123</v>
+        <v>2.07026219367981</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371814250946</v>
+        <v>1.87371826171875</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.8387770652771</v>
+        <v>1.83877718448639</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923282623291</v>
+        <v>1.93923306465149</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302692890167</v>
+        <v>1.91302716732025</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314477443695</v>
+        <v>1.84314453601837</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.55488038063049</v>
+        <v>1.5548802614212</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G156" t="n">
-        <v>1.6247626543045</v>
+        <v>1.62476277351379</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235085964203</v>
+        <v>1.57235097885132</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602747440338</v>
+        <v>1.61602735519409</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843903064728</v>
+        <v>1.66843891143799</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015961170197</v>
+        <v>1.76015973091125</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992635726929</v>
+        <v>1.71992647647858</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072888374329</v>
+        <v>1.71072900295258</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153152942657</v>
+        <v>1.70153141021729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554404258728</v>
+        <v>1.65554416179657</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576070308685</v>
+        <v>1.59576058387756</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421893119812</v>
+        <v>1.38421881198883</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714921474457</v>
+        <v>1.63714909553528</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582386493683</v>
+        <v>1.36582398414612</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662639141083</v>
+        <v>1.35662651062012</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -32560,6 +32560,32 @@
         <v>1.44000005722046</v>
       </c>
       <c r="H1238" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1239" t="n">
+        <v>39679</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>1.41499996185303</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>1.39999997615814</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="H1239" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668804168701</v>
+        <v>2.33668828010559</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.52900004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>2.209153175354</v>
+        <v>2.20915341377258</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818831443787</v>
+        <v>2.18818855285645</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267398834229</v>
+        <v>2.12267374992371</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911521911621</v>
+        <v>2.00911498069763</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360053539276</v>
+        <v>1.94360041618347</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486499786377</v>
+        <v>1.93486511707306</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164438247681</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92612993717194</v>
+        <v>1.92613005638123</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360053539276</v>
+        <v>1.94360041618347</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267398834229</v>
+        <v>2.12267374992371</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761470794678</v>
+        <v>2.15761494636536</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911521911621</v>
+        <v>2.00911498069763</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555656909943</v>
+        <v>1.89555644989014</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061561107635</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061561107635</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164438247681</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164438247681</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.16635036468506</v>
+        <v>2.16635012626648</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02221822738647</v>
+        <v>2.0222179889679</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371826171875</v>
+        <v>1.87371814250946</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.83877718448639</v>
+        <v>1.83877730369568</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923306465149</v>
+        <v>1.9392329454422</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.9304975271225</v>
+        <v>1.93049764633179</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440947532654</v>
+        <v>1.83440935611725</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81693875789642</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510080814362</v>
+        <v>1.79510068893433</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061561107635</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302716732025</v>
+        <v>1.91302704811096</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.81693875789642</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74530959129333</v>
+        <v>1.74530947208405</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108615875244</v>
+        <v>1.58108627796173</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.5548802614212</v>
+        <v>1.55488038063049</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108615875244</v>
+        <v>1.58108627796173</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.63699209690094</v>
+        <v>1.63699197769165</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843891143799</v>
+        <v>1.66843903064728</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004176616669</v>
+        <v>1.83004188537598</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440947532654</v>
+        <v>1.83440935611725</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.81693875789642</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.81693875789642</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510080814362</v>
+        <v>1.79510068893433</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -32586,6 +32586,32 @@
         <v>1.37000000476837</v>
       </c>
       <c r="H1239" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1240" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1240" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="H1240" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668828010559</v>
+        <v>2.33668804168701</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.52900004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>2.20915341377258</v>
+        <v>2.209153175354</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818855285645</v>
+        <v>2.18818831443787</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486511707306</v>
+        <v>1.93486499786377</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92613005638123</v>
+        <v>1.92612993717194</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761494636536</v>
+        <v>2.15761470794678</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555644989014</v>
+        <v>1.89555656909943</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.16635012626648</v>
+        <v>2.16635036468506</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>2.0222179889679</v>
+        <v>2.02221822738647</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371814250946</v>
+        <v>1.87371826171875</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.83877730369568</v>
+        <v>1.83877718448639</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.9392329454422</v>
+        <v>1.93923306465149</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.93049764633179</v>
+        <v>1.9304975271225</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302704811096</v>
+        <v>1.91302716732025</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74530947208405</v>
+        <v>1.74530959129333</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.55488038063049</v>
+        <v>1.5548802614212</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.63699197769165</v>
+        <v>1.63699209690094</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843903064728</v>
+        <v>1.66843891143799</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004188537598</v>
+        <v>1.83004176616669</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -32612,6 +32612,32 @@
         <v>1.35000002384186</v>
       </c>
       <c r="H1240" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1241" t="n">
+        <v>130</v>
+      </c>
+      <c r="C1241" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>1.36000001430511</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="G1241" t="n">
+        <v>1.37000000476837</v>
+      </c>
+      <c r="H1241" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749733924866</v>
+        <v>2.22749710083008</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2231297492981</v>
+        <v>2.22312951087952</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818855285645</v>
+        <v>2.18818831443787</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04405641555786</v>
+        <v>2.04405617713928</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.375</v>
       </c>
       <c r="G18" t="n">
-        <v>2.07463002204895</v>
+        <v>2.07462978363037</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G20" t="n">
-        <v>2.07899761199951</v>
+        <v>2.07899737358093</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>2.01785063743591</v>
+        <v>2.01785039901733</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G30" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82567405700684</v>
+        <v>1.82567417621613</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486523628235</v>
+        <v>1.93486499786377</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.88245356082916</v>
+        <v>1.88245368003845</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8475124835968</v>
+        <v>1.84751236438751</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.00474739074707</v>
+        <v>2.00474762916565</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.99164462089539</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92612969875336</v>
+        <v>1.92612993717194</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>2.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.18382096290588</v>
+        <v>2.1838207244873</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G50" t="n">
-        <v>2.14887952804565</v>
+        <v>2.14887976646423</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761494636536</v>
+        <v>2.15761470794678</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12704110145569</v>
+        <v>2.12704133987427</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176234722137</v>
+        <v>1.92176246643066</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G58" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555644989014</v>
+        <v>1.89555656909943</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.86498296260834</v>
+        <v>1.86498284339905</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.99164462089539</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.05279159545898</v>
+        <v>2.05279135704041</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026171684265</v>
+        <v>2.07026219367981</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>2.01785063743591</v>
+        <v>2.01785039901733</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.07899761199951</v>
+        <v>2.07899737358093</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.99164462089539</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G78" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.08336520195007</v>
+        <v>2.08336496353149</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.07899761199951</v>
+        <v>2.07899737358093</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G85" t="n">
-        <v>1.80383598804474</v>
+        <v>1.80383610725403</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371814250946</v>
+        <v>1.87371826171875</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>1.91739451885223</v>
+        <v>1.91739463806152</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G91" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G92" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G94" t="n">
-        <v>1.7557920217514</v>
+        <v>1.75579190254211</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>1.7557920217514</v>
+        <v>1.75579190254211</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G102" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923282623291</v>
+        <v>1.93923306465149</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.93049776554108</v>
+        <v>1.9304975271225</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G111" t="n">
-        <v>1.88245356082916</v>
+        <v>1.88245368003845</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G112" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.81257140636444</v>
+        <v>1.81257128715515</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G118" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>1.7557920217514</v>
+        <v>1.75579190254211</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>1.76889503002167</v>
+        <v>1.76889491081238</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302704811096</v>
+        <v>1.91302716732025</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314465522766</v>
+        <v>1.84314453601837</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82567405700684</v>
+        <v>1.82567417621613</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G142" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G156" t="n">
-        <v>1.6247626543045</v>
+        <v>1.62476277351379</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69639194011688</v>
+        <v>1.69639205932617</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843903064728</v>
+        <v>1.66843891143799</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>1.72085070610046</v>
+        <v>1.72085082530975</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G172" t="n">
-        <v>1.75142431259155</v>
+        <v>1.75142443180084</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004188537598</v>
+        <v>1.83004176616669</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G177" t="n">
-        <v>1.80383598804474</v>
+        <v>1.80383610725403</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015961170197</v>
+        <v>1.76015973091125</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G182" t="n">
-        <v>1.72085070610046</v>
+        <v>1.72085082530975</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992635726929</v>
+        <v>1.71992647647858</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072888374329</v>
+        <v>1.71072900295258</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153152942657</v>
+        <v>1.70153141021729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554404258728</v>
+        <v>1.65554416179657</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576070308685</v>
+        <v>1.59576058387756</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421893119812</v>
+        <v>1.38421881198883</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714921474457</v>
+        <v>1.63714909553528</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582386493683</v>
+        <v>1.36582398414612</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662639141083</v>
+        <v>1.35662651062012</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -32690,6 +32690,32 @@
         <v>1.31500005722046</v>
       </c>
       <c r="H1243" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1244" t="n">
+        <v>4368</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>1.36500000953674</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G1244" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="H1244" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -29046,8 +29046,31 @@
       <c r="E1247" t="n">
         <v>1.36500000953674</v>
       </c>
-      <c r="F1247"/>
+      <c r="F1247" t="n">
+        <v>1.37999999523163</v>
+      </c>
       <c r="G1247" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1248" t="n">
+        <v>12558</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>1.41999995708466</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>1.37999999523163</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>1.39499998092651</v>
+      </c>
+      <c r="F1248"/>
+      <c r="G1248" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -29069,8 +29069,31 @@
       <c r="E1248" t="n">
         <v>1.39499998092651</v>
       </c>
-      <c r="F1248"/>
+      <c r="F1248" t="n">
+        <v>1.38999998569489</v>
+      </c>
       <c r="G1248" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1249" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>1.35500001907349</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>1.35500001907349</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>1.35500001907349</v>
+      </c>
+      <c r="F1249"/>
+      <c r="G1249" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -29092,8 +29092,31 @@
       <c r="E1249" t="n">
         <v>1.35500001907349</v>
       </c>
-      <c r="F1249"/>
+      <c r="F1249" t="n">
+        <v>1.35500001907349</v>
+      </c>
       <c r="G1249" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1250" t="n">
+        <v>4541</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>1.33000004291534</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>1.31500005722046</v>
+      </c>
+      <c r="F1250"/>
+      <c r="G1250" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -29115,8 +29115,31 @@
       <c r="E1250" t="n">
         <v>1.31500005722046</v>
       </c>
-      <c r="F1250"/>
+      <c r="F1250" t="n">
+        <v>1.28999996185303</v>
+      </c>
       <c r="G1250" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1251" t="n">
+        <v>15175</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>1.34500002861023</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>1.30499994754791</v>
+      </c>
+      <c r="F1251"/>
+      <c r="G1251" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -29145,6 +29145,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1252">
+      <c r="A1252" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1252" t="n">
+        <v>6108</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>1.31500005722046</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>1.3400000333786</v>
+      </c>
+      <c r="G1252" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -29168,6 +29168,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B1253" t="n">
+        <v>1900</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>1.33500003814697</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="G1253" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -447,7 +447,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668828010559</v>
+        <v>2.33668804168701</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.52900004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>2.20915341377258</v>
+        <v>2.209153175354</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818855285645</v>
+        <v>2.18818831443787</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486511707306</v>
+        <v>1.93486499786377</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92613005638123</v>
+        <v>1.92612993717194</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761494636536</v>
+        <v>2.15761470794678</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555644989014</v>
+        <v>1.89555656909943</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.16635012626648</v>
+        <v>2.16635036468506</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>2.0222179889679</v>
+        <v>2.02221822738647</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371814250946</v>
+        <v>1.87371826171875</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.83877730369568</v>
+        <v>1.83877718448639</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.9392329454422</v>
+        <v>1.93923306465149</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.93049764633179</v>
+        <v>1.9304975271225</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302704811096</v>
+        <v>1.91302716732025</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74530947208405</v>
+        <v>1.74530959129333</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.55488038063049</v>
+        <v>1.5548802614212</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.63699197769165</v>
+        <v>1.63699209690094</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843903064728</v>
+        <v>1.66843891143799</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004188537598</v>
+        <v>1.83004176616669</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.81693887710571</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -33002,6 +33002,32 @@
         <v>1.30999994277954</v>
       </c>
       <c r="H1255" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1256" t="n">
+        <v>3798</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>1.32500004768372</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="H1256" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668828010559</v>
+        <v>2.33668804168701</v>
       </c>
       <c r="H3" t="n">
         <v>191052</v>
@@ -572,7 +572,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>2.22312951087952</v>
+        <v>2.2231297492981</v>
       </c>
       <c r="H7" t="n">
         <v>31322</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H9" t="n">
         <v>39782</v>
@@ -688,7 +688,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14014434814453</v>
+        <v>2.14014458656311</v>
       </c>
       <c r="H11" t="n">
         <v>7333</v>
@@ -746,7 +746,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H13" t="n">
         <v>3783</v>
@@ -775,7 +775,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0440559387207</v>
+        <v>2.04405641555786</v>
       </c>
       <c r="H14" t="n">
         <v>4196</v>
@@ -804,7 +804,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>1.86935067176819</v>
+        <v>1.8693505525589</v>
       </c>
       <c r="H15" t="n">
         <v>81372</v>
@@ -891,7 +891,7 @@
         <v>2.375</v>
       </c>
       <c r="G18" t="n">
-        <v>2.07462978363037</v>
+        <v>2.07463002204895</v>
       </c>
       <c r="H18" t="n">
         <v>3820</v>
@@ -920,7 +920,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H19" t="n">
         <v>10225</v>
@@ -949,7 +949,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G20" t="n">
-        <v>2.07899737358093</v>
+        <v>2.07899761199951</v>
       </c>
       <c r="H20" t="n">
         <v>38604</v>
@@ -1007,7 +1007,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267398834229</v>
+        <v>2.12267374992371</v>
       </c>
       <c r="H22" t="n">
         <v>64202</v>
@@ -1094,7 +1094,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911521911621</v>
+        <v>2.00911498069763</v>
       </c>
       <c r="H25" t="n">
         <v>22357</v>
@@ -1123,7 +1123,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>2.01785039901733</v>
+        <v>2.01785063743591</v>
       </c>
       <c r="H26" t="n">
         <v>26413</v>
@@ -1152,7 +1152,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H27" t="n">
         <v>18554</v>
@@ -1210,7 +1210,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360041618347</v>
       </c>
       <c r="H29" t="n">
         <v>7100</v>
@@ -1239,7 +1239,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G30" t="n">
-        <v>1.86935067176819</v>
+        <v>1.8693505525589</v>
       </c>
       <c r="H30" t="n">
         <v>13323</v>
@@ -1268,7 +1268,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82567417621613</v>
+        <v>1.82567405700684</v>
       </c>
       <c r="H31" t="n">
         <v>9150</v>
@@ -1384,7 +1384,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H35" t="n">
         <v>551</v>
@@ -1413,7 +1413,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.88245368003845</v>
+        <v>1.88245356082916</v>
       </c>
       <c r="H36" t="n">
         <v>10145</v>
@@ -1442,7 +1442,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G37" t="n">
-        <v>1.84751236438751</v>
+        <v>1.8475124835968</v>
       </c>
       <c r="H37" t="n">
         <v>6948</v>
@@ -1558,7 +1558,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H41" t="n">
         <v>4717</v>
@@ -1587,7 +1587,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.00474762916565</v>
+        <v>2.00474739074707</v>
       </c>
       <c r="H42" t="n">
         <v>890</v>
@@ -1645,7 +1645,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164462089539</v>
       </c>
       <c r="H44" t="n">
         <v>4404</v>
@@ -1674,7 +1674,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92612993717194</v>
+        <v>1.92612969875336</v>
       </c>
       <c r="H45" t="n">
         <v>842</v>
@@ -1703,7 +1703,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360041618347</v>
       </c>
       <c r="H46" t="n">
         <v>21305</v>
@@ -1732,7 +1732,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14014434814453</v>
+        <v>2.14014458656311</v>
       </c>
       <c r="H47" t="n">
         <v>72616</v>
@@ -1761,7 +1761,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267398834229</v>
+        <v>2.12267374992371</v>
       </c>
       <c r="H48" t="n">
         <v>72728</v>
@@ -1790,7 +1790,7 @@
         <v>2.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.1838207244873</v>
+        <v>2.18382096290588</v>
       </c>
       <c r="H49" t="n">
         <v>114387</v>
@@ -1819,7 +1819,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G50" t="n">
-        <v>2.14887976646423</v>
+        <v>2.14887952804565</v>
       </c>
       <c r="H50" t="n">
         <v>7396</v>
@@ -1877,7 +1877,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12704133987427</v>
+        <v>2.12704110145569</v>
       </c>
       <c r="H52" t="n">
         <v>44983</v>
@@ -1906,7 +1906,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H53" t="n">
         <v>7775</v>
@@ -1935,7 +1935,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911521911621</v>
+        <v>2.00911498069763</v>
       </c>
       <c r="H54" t="n">
         <v>23493</v>
@@ -2022,7 +2022,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176222801208</v>
+        <v>1.92176234722137</v>
       </c>
       <c r="H57" t="n">
         <v>12475</v>
@@ -2051,7 +2051,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G58" t="n">
-        <v>1.8780859708786</v>
+        <v>1.87808609008789</v>
       </c>
       <c r="H58" t="n">
         <v>59820</v>
@@ -2138,7 +2138,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H61" t="n">
         <v>15420</v>
@@ -2167,7 +2167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2196,7 +2196,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.86498284339905</v>
+        <v>1.86498296260834</v>
       </c>
       <c r="H63" t="n">
         <v>9001</v>
@@ -2225,7 +2225,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H64" t="n">
         <v>27250</v>
@@ -2254,7 +2254,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164462089539</v>
       </c>
       <c r="H65" t="n">
         <v>62307</v>
@@ -2283,7 +2283,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.05279135704041</v>
+        <v>2.05279159545898</v>
       </c>
       <c r="H66" t="n">
         <v>299677</v>
@@ -2312,7 +2312,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026195526123</v>
+        <v>2.07026171684265</v>
       </c>
       <c r="H67" t="n">
         <v>164735</v>
@@ -2370,7 +2370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H69" t="n">
         <v>10560</v>
@@ -2399,7 +2399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H70" t="n">
         <v>2080</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>2.01785039901733</v>
+        <v>2.01785063743591</v>
       </c>
       <c r="H72" t="n">
         <v>5325</v>
@@ -2486,7 +2486,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.07899737358093</v>
+        <v>2.07899761199951</v>
       </c>
       <c r="H73" t="n">
         <v>4627</v>
@@ -2515,7 +2515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164462089539</v>
       </c>
       <c r="H74" t="n">
         <v>72717</v>
@@ -2631,7 +2631,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G78" t="n">
-        <v>2.14014434814453</v>
+        <v>2.14014458656311</v>
       </c>
       <c r="H78" t="n">
         <v>29301</v>
@@ -2660,7 +2660,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>2.14014434814453</v>
+        <v>2.14014458656311</v>
       </c>
       <c r="H79" t="n">
         <v>16750</v>
@@ -2718,7 +2718,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.08336496353149</v>
+        <v>2.08336520195007</v>
       </c>
       <c r="H81" t="n">
         <v>6800</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.07899737358093</v>
+        <v>2.07899761199951</v>
       </c>
       <c r="H82" t="n">
         <v>4785</v>
@@ -2805,7 +2805,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>1.8780859708786</v>
+        <v>1.87808609008789</v>
       </c>
       <c r="H84" t="n">
         <v>40084</v>
@@ -2834,7 +2834,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G85" t="n">
-        <v>1.80383610725403</v>
+        <v>1.80383598804474</v>
       </c>
       <c r="H85" t="n">
         <v>50746</v>
@@ -2892,7 +2892,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.79946827888489</v>
+        <v>1.79946839809418</v>
       </c>
       <c r="H87" t="n">
         <v>6821</v>
@@ -2921,7 +2921,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H88" t="n">
         <v>42972</v>
@@ -2950,7 +2950,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>1.91739463806152</v>
+        <v>1.91739451885223</v>
       </c>
       <c r="H89" t="n">
         <v>26018</v>
@@ -2979,7 +2979,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>1.8082035779953</v>
+        <v>1.80820345878601</v>
       </c>
       <c r="H90" t="n">
         <v>84825</v>
@@ -3008,7 +3008,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G91" t="n">
-        <v>1.78199779987335</v>
+        <v>1.78199768066406</v>
       </c>
       <c r="H91" t="n">
         <v>67557</v>
@@ -3037,7 +3037,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G92" t="n">
-        <v>1.79946827888489</v>
+        <v>1.79946839809418</v>
       </c>
       <c r="H92" t="n">
         <v>59108</v>
@@ -3095,7 +3095,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G94" t="n">
-        <v>1.75579190254211</v>
+        <v>1.7557920217514</v>
       </c>
       <c r="H94" t="n">
         <v>53564</v>
@@ -3182,7 +3182,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>1.75579190254211</v>
+        <v>1.7557920217514</v>
       </c>
       <c r="H97" t="n">
         <v>11316</v>
@@ -3240,7 +3240,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>1.8082035779953</v>
+        <v>1.80820345878601</v>
       </c>
       <c r="H99" t="n">
         <v>12875</v>
@@ -3269,7 +3269,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.8387770652771</v>
+        <v>1.83877718448639</v>
       </c>
       <c r="H100" t="n">
         <v>42528</v>
@@ -3298,7 +3298,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H101" t="n">
         <v>278213</v>
@@ -3327,7 +3327,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G102" t="n">
-        <v>1.8082035779953</v>
+        <v>1.80820345878601</v>
       </c>
       <c r="H102" t="n">
         <v>16708</v>
@@ -3414,7 +3414,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.9304975271225</v>
+        <v>1.93049776554108</v>
       </c>
       <c r="H105" t="n">
         <v>93326</v>
@@ -3443,7 +3443,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.8780859708786</v>
+        <v>1.87808609008789</v>
       </c>
       <c r="H106" t="n">
         <v>43370</v>
@@ -3472,7 +3472,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440947532654</v>
+        <v>1.83440935611725</v>
       </c>
       <c r="H107" t="n">
         <v>7685</v>
@@ -3501,7 +3501,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.86935067176819</v>
+        <v>1.8693505525589</v>
       </c>
       <c r="H108" t="n">
         <v>4800</v>
@@ -3530,7 +3530,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.86935067176819</v>
+        <v>1.8693505525589</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H110" t="n">
         <v>3088</v>
@@ -3588,7 +3588,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G111" t="n">
-        <v>1.88245368003845</v>
+        <v>1.88245356082916</v>
       </c>
       <c r="H111" t="n">
         <v>3762</v>
@@ -3617,7 +3617,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G112" t="n">
-        <v>1.8780859708786</v>
+        <v>1.87808609008789</v>
       </c>
       <c r="H112" t="n">
         <v>60471</v>
@@ -3675,7 +3675,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.81257128715515</v>
+        <v>1.81257140636444</v>
       </c>
       <c r="H114" t="n">
         <v>2950</v>
@@ -3704,7 +3704,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>1.8780859708786</v>
+        <v>1.87808609008789</v>
       </c>
       <c r="H115" t="n">
         <v>9850</v>
@@ -3733,7 +3733,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>1.8780859708786</v>
+        <v>1.87808609008789</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G118" t="n">
-        <v>1.8082035779953</v>
+        <v>1.80820345878601</v>
       </c>
       <c r="H118" t="n">
         <v>17395</v>
@@ -3820,7 +3820,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>1.75579190254211</v>
+        <v>1.7557920217514</v>
       </c>
       <c r="H119" t="n">
         <v>17414</v>
@@ -3849,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H120" t="n">
         <v>8950</v>
@@ -3907,7 +3907,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H122" t="n">
         <v>16909</v>
@@ -3936,7 +3936,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>1.76889491081238</v>
+        <v>1.76889503002167</v>
       </c>
       <c r="H123" t="n">
         <v>55749</v>
@@ -3965,7 +3965,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510080814362</v>
+        <v>1.79510068893433</v>
       </c>
       <c r="H124" t="n">
         <v>297933</v>
@@ -3994,7 +3994,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H125" t="n">
         <v>101033</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302692890167</v>
+        <v>1.91302704811096</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H127" t="n">
         <v>13630</v>
@@ -4139,7 +4139,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>1.79946827888489</v>
+        <v>1.79946839809418</v>
       </c>
       <c r="H130" t="n">
         <v>1499</v>
@@ -4168,7 +4168,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H131" t="n">
         <v>7054</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314477443695</v>
+        <v>1.84314465522766</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4342,7 +4342,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H137" t="n">
         <v>1563</v>
@@ -4458,7 +4458,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82567417621613</v>
+        <v>1.82567405700684</v>
       </c>
       <c r="H141" t="n">
         <v>39804</v>
@@ -4487,7 +4487,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G142" t="n">
-        <v>1.79946827888489</v>
+        <v>1.79946839809418</v>
       </c>
       <c r="H142" t="n">
         <v>9236</v>
@@ -4516,7 +4516,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79946827888489</v>
+        <v>1.79946839809418</v>
       </c>
       <c r="H143" t="n">
         <v>1000</v>
@@ -4603,7 +4603,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>1.78199779987335</v>
+        <v>1.78199768066406</v>
       </c>
       <c r="H146" t="n">
         <v>4619</v>
@@ -4632,7 +4632,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H147" t="n">
         <v>3822</v>
@@ -4661,7 +4661,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>1.79946827888489</v>
+        <v>1.79946839809418</v>
       </c>
       <c r="H148" t="n">
         <v>2244</v>
@@ -4690,7 +4690,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79946827888489</v>
+        <v>1.79946839809418</v>
       </c>
       <c r="H149" t="n">
         <v>8350</v>
@@ -4719,7 +4719,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H150" t="n">
         <v>43320</v>
@@ -4806,7 +4806,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H153" t="n">
         <v>138668</v>
@@ -4835,7 +4835,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.55488038063049</v>
+        <v>1.5548802614212</v>
       </c>
       <c r="H154" t="n">
         <v>63112</v>
@@ -4922,7 +4922,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235085964203</v>
+        <v>1.57235097885132</v>
       </c>
       <c r="H157" t="n">
         <v>46024</v>
@@ -5038,7 +5038,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H161" t="n">
         <v>13350</v>
@@ -5096,7 +5096,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69639205932617</v>
+        <v>1.69639194011688</v>
       </c>
       <c r="H163" t="n">
         <v>8671</v>
@@ -5154,7 +5154,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602747440338</v>
+        <v>1.61602735519409</v>
       </c>
       <c r="H165" t="n">
         <v>10225</v>
@@ -5299,7 +5299,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>1.72085082530975</v>
+        <v>1.72085070610046</v>
       </c>
       <c r="H170" t="n">
         <v>14591</v>
@@ -5328,7 +5328,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H171" t="n">
         <v>25750</v>
@@ -5357,7 +5357,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G172" t="n">
-        <v>1.75142443180084</v>
+        <v>1.75142431259155</v>
       </c>
       <c r="H172" t="n">
         <v>2416</v>
@@ -5386,7 +5386,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004176616669</v>
+        <v>1.83004188537598</v>
       </c>
       <c r="H173" t="n">
         <v>9852</v>
@@ -5415,7 +5415,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440947532654</v>
+        <v>1.83440935611725</v>
       </c>
       <c r="H174" t="n">
         <v>1450</v>
@@ -5444,7 +5444,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H175" t="n">
         <v>5050</v>
@@ -5502,7 +5502,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G177" t="n">
-        <v>1.80383610725403</v>
+        <v>1.80383598804474</v>
       </c>
       <c r="H177" t="n">
         <v>3406</v>
@@ -5531,7 +5531,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H178" t="n">
         <v>14700</v>
@@ -5560,7 +5560,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510080814362</v>
+        <v>1.79510068893433</v>
       </c>
       <c r="H179" t="n">
         <v>1733</v>
@@ -5618,7 +5618,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>1.78199779987335</v>
+        <v>1.78199768066406</v>
       </c>
       <c r="H181" t="n">
         <v>1000</v>
@@ -5647,7 +5647,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G182" t="n">
-        <v>1.72085082530975</v>
+        <v>1.72085070610046</v>
       </c>
       <c r="H182" t="n">
         <v>2460</v>
@@ -5676,7 +5676,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H183" t="n">
         <v>8218</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>1.78199779987335</v>
+        <v>1.78199768066406</v>
       </c>
       <c r="H184" t="n">
         <v>289</v>
@@ -36828,6 +36828,35 @@
         <v>967</v>
       </c>
       <c r="I1257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1258" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>2768</v>
+      </c>
+      <c r="I1258" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668804168701</v>
+        <v>2.33668828010559</v>
       </c>
       <c r="H3" t="n">
         <v>191052</v>
@@ -485,7 +485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749733924866</v>
+        <v>2.22749710083008</v>
       </c>
       <c r="H4" t="n">
         <v>60317</v>
@@ -601,7 +601,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818855285645</v>
+        <v>2.18818879127502</v>
       </c>
       <c r="H8" t="n">
         <v>38845</v>
@@ -688,7 +688,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H11" t="n">
         <v>7333</v>
@@ -717,7 +717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H12" t="n">
         <v>21519</v>
@@ -804,7 +804,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H15" t="n">
         <v>81372</v>
@@ -862,7 +862,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H17" t="n">
         <v>65997</v>
@@ -891,7 +891,7 @@
         <v>2.375</v>
       </c>
       <c r="G18" t="n">
-        <v>2.07463002204895</v>
+        <v>2.07462978363037</v>
       </c>
       <c r="H18" t="n">
         <v>3820</v>
@@ -978,7 +978,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H21" t="n">
         <v>6307</v>
@@ -1036,7 +1036,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H23" t="n">
         <v>9285</v>
@@ -1123,7 +1123,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G26" t="n">
-        <v>2.01785063743591</v>
+        <v>2.01785039901733</v>
       </c>
       <c r="H26" t="n">
         <v>26413</v>
@@ -1181,7 +1181,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H28" t="n">
         <v>33355</v>
@@ -1239,7 +1239,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G30" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H30" t="n">
         <v>13323</v>
@@ -1268,7 +1268,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G31" t="n">
-        <v>1.82567405700684</v>
+        <v>1.82567417621613</v>
       </c>
       <c r="H31" t="n">
         <v>9150</v>
@@ -1297,7 +1297,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486523628235</v>
+        <v>1.93486535549164</v>
       </c>
       <c r="H32" t="n">
         <v>5405</v>
@@ -1471,7 +1471,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H38" t="n">
         <v>17244</v>
@@ -1587,7 +1587,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G42" t="n">
-        <v>2.00474739074707</v>
+        <v>2.00474762916565</v>
       </c>
       <c r="H42" t="n">
         <v>890</v>
@@ -1674,7 +1674,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92612969875336</v>
+        <v>1.92612981796265</v>
       </c>
       <c r="H45" t="n">
         <v>842</v>
@@ -1732,7 +1732,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G47" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H47" t="n">
         <v>72616</v>
@@ -1819,7 +1819,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G50" t="n">
-        <v>2.14887952804565</v>
+        <v>2.14887976646423</v>
       </c>
       <c r="H50" t="n">
         <v>7396</v>
@@ -2196,7 +2196,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G63" t="n">
-        <v>1.86498296260834</v>
+        <v>1.86498284339905</v>
       </c>
       <c r="H63" t="n">
         <v>9001</v>
@@ -2283,7 +2283,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G66" t="n">
-        <v>2.05279159545898</v>
+        <v>2.05279135704041</v>
       </c>
       <c r="H66" t="n">
         <v>299677</v>
@@ -2312,7 +2312,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026171684265</v>
+        <v>2.07026195526123</v>
       </c>
       <c r="H67" t="n">
         <v>164735</v>
@@ -2341,7 +2341,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>2.13140916824341</v>
+        <v>2.13140940666199</v>
       </c>
       <c r="H68" t="n">
         <v>48909</v>
@@ -2457,7 +2457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>2.01785063743591</v>
+        <v>2.01785039901733</v>
       </c>
       <c r="H72" t="n">
         <v>5325</v>
@@ -2602,7 +2602,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.13140916824341</v>
+        <v>2.13140940666199</v>
       </c>
       <c r="H77" t="n">
         <v>43135</v>
@@ -2631,7 +2631,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G78" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H78" t="n">
         <v>29301</v>
@@ -2660,7 +2660,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G79" t="n">
-        <v>2.14014458656311</v>
+        <v>2.14014434814453</v>
       </c>
       <c r="H79" t="n">
         <v>16750</v>
@@ -2689,7 +2689,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H80" t="n">
         <v>3341</v>
@@ -2718,7 +2718,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G81" t="n">
-        <v>2.08336520195007</v>
+        <v>2.08336496353149</v>
       </c>
       <c r="H81" t="n">
         <v>6800</v>
@@ -2776,7 +2776,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02221822738647</v>
+        <v>2.0222179889679</v>
       </c>
       <c r="H83" t="n">
         <v>2250</v>
@@ -2863,7 +2863,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371814250946</v>
+        <v>1.87371802330017</v>
       </c>
       <c r="H86" t="n">
         <v>7811</v>
@@ -2892,7 +2892,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G87" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H87" t="n">
         <v>6821</v>
@@ -2979,7 +2979,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G90" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H90" t="n">
         <v>84825</v>
@@ -3037,7 +3037,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G92" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H92" t="n">
         <v>59108</v>
@@ -3066,7 +3066,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H93" t="n">
         <v>27514</v>
@@ -3095,7 +3095,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G94" t="n">
-        <v>1.7557920217514</v>
+        <v>1.75579190254211</v>
       </c>
       <c r="H94" t="n">
         <v>53564</v>
@@ -3153,7 +3153,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H96" t="n">
         <v>18344</v>
@@ -3182,7 +3182,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G97" t="n">
-        <v>1.7557920217514</v>
+        <v>1.75579190254211</v>
       </c>
       <c r="H97" t="n">
         <v>11316</v>
@@ -3211,7 +3211,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H98" t="n">
         <v>35330</v>
@@ -3240,7 +3240,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G99" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H99" t="n">
         <v>12875</v>
@@ -3327,7 +3327,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G102" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H102" t="n">
         <v>16708</v>
@@ -3356,7 +3356,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G103" t="n">
-        <v>1.82130658626556</v>
+        <v>1.82130646705627</v>
       </c>
       <c r="H103" t="n">
         <v>23656</v>
@@ -3385,7 +3385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923282623291</v>
+        <v>1.9392329454422</v>
       </c>
       <c r="H104" t="n">
         <v>63970</v>
@@ -3414,7 +3414,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.93049776554108</v>
+        <v>1.93049764633179</v>
       </c>
       <c r="H105" t="n">
         <v>93326</v>
@@ -3501,7 +3501,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H108" t="n">
         <v>4800</v>
@@ -3530,7 +3530,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G109" t="n">
-        <v>1.8693505525589</v>
+        <v>1.86935067176819</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>1.82130658626556</v>
+        <v>1.82130646705627</v>
       </c>
       <c r="H113" t="n">
         <v>4748</v>
@@ -3675,7 +3675,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>1.81257140636444</v>
+        <v>1.81257128715515</v>
       </c>
       <c r="H114" t="n">
         <v>2950</v>
@@ -3762,7 +3762,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.82130658626556</v>
+        <v>1.82130646705627</v>
       </c>
       <c r="H117" t="n">
         <v>3428</v>
@@ -3791,7 +3791,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G118" t="n">
-        <v>1.80820345878601</v>
+        <v>1.8082035779953</v>
       </c>
       <c r="H118" t="n">
         <v>17395</v>
@@ -3820,7 +3820,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>1.7557920217514</v>
+        <v>1.75579190254211</v>
       </c>
       <c r="H119" t="n">
         <v>17414</v>
@@ -3878,7 +3878,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>1.82130658626556</v>
+        <v>1.82130646705627</v>
       </c>
       <c r="H121" t="n">
         <v>66730</v>
@@ -3936,7 +3936,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>1.76889503002167</v>
+        <v>1.76889491081238</v>
       </c>
       <c r="H123" t="n">
         <v>55749</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302704811096</v>
+        <v>1.91302716732025</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4081,7 +4081,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82130658626556</v>
+        <v>1.82130646705627</v>
       </c>
       <c r="H128" t="n">
         <v>2764</v>
@@ -4110,7 +4110,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82130658626556</v>
+        <v>1.82130646705627</v>
       </c>
       <c r="H129" t="n">
         <v>4350</v>
@@ -4139,7 +4139,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G130" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H130" t="n">
         <v>1499</v>
@@ -4226,7 +4226,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>1.82130658626556</v>
+        <v>1.82130646705627</v>
       </c>
       <c r="H133" t="n">
         <v>35730</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314465522766</v>
+        <v>1.84314453601837</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4371,7 +4371,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H138" t="n">
         <v>3100</v>
@@ -4458,7 +4458,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G141" t="n">
-        <v>1.82567405700684</v>
+        <v>1.82567417621613</v>
       </c>
       <c r="H141" t="n">
         <v>39804</v>
@@ -4487,7 +4487,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G142" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H142" t="n">
         <v>9236</v>
@@ -4516,7 +4516,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H143" t="n">
         <v>1000</v>
@@ -4661,7 +4661,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G148" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H148" t="n">
         <v>2244</v>
@@ -4690,7 +4690,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G149" t="n">
-        <v>1.79946839809418</v>
+        <v>1.79946827888489</v>
       </c>
       <c r="H149" t="n">
         <v>8350</v>
@@ -4806,7 +4806,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108615875244</v>
+        <v>1.58108627796173</v>
       </c>
       <c r="H153" t="n">
         <v>138668</v>
@@ -4835,7 +4835,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.5548802614212</v>
+        <v>1.55488038063049</v>
       </c>
       <c r="H154" t="n">
         <v>63112</v>
@@ -4864,7 +4864,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>1.4884922504425</v>
+        <v>1.48849213123322</v>
       </c>
       <c r="H155" t="n">
         <v>15100</v>
@@ -5038,7 +5038,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108615875244</v>
+        <v>1.58108627796173</v>
       </c>
       <c r="H161" t="n">
         <v>13350</v>
@@ -5096,7 +5096,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G163" t="n">
-        <v>1.69639194011688</v>
+        <v>1.69639205932617</v>
       </c>
       <c r="H163" t="n">
         <v>8671</v>
@@ -5125,7 +5125,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.63699209690094</v>
+        <v>1.63699197769165</v>
       </c>
       <c r="H164" t="n">
         <v>10490</v>
@@ -5299,7 +5299,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G170" t="n">
-        <v>1.72085070610046</v>
+        <v>1.72085082530975</v>
       </c>
       <c r="H170" t="n">
         <v>14591</v>
@@ -5357,7 +5357,7 @@
         <v>2.00500011444092</v>
       </c>
       <c r="G172" t="n">
-        <v>1.75142431259155</v>
+        <v>1.75142443180084</v>
       </c>
       <c r="H172" t="n">
         <v>2416</v>
@@ -5589,7 +5589,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015961170197</v>
+        <v>1.76015973091125</v>
       </c>
       <c r="H180" t="n">
         <v>15133</v>
@@ -5647,7 +5647,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G182" t="n">
-        <v>1.72085070610046</v>
+        <v>1.72085082530975</v>
       </c>
       <c r="H182" t="n">
         <v>2460</v>
@@ -5734,7 +5734,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G185" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H185" t="n">
         <v>3794</v>
@@ -5763,7 +5763,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G187" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G193" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G194" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G197" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G198" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G199" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G200" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G201" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G202" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G204" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G206" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G210" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G212" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G213" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G214" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G216" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G217" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G223" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G224" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G225" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G226" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G227" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G230" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G231" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G232" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G235" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G236" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G237" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G239" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G241" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G242" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G244" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G245" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G246" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G249" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G250" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G253" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G254" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G256" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G257" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G259" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G260" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G261" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G262" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G263" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G265" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G266" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G267" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G270" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G271" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G272" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G278" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G279" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G280" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G281" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G282" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G283" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G285" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G286" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G287" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G288" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G289" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G290" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G291" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G294" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G295" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G299" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G302" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G303" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G304" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G305" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G306" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G307" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G311" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G316" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G317" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G318" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G320" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G322" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G323" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G324" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G327" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G328" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G329" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G330" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G332" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G333" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G336" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G337" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G338" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G340" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G341" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G342" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G343" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G344" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G346" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G348" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G349" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G351" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G354" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G355" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G359" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G362" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G365" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G366" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G367" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G368" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G369" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G370" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G371" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G372" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G374" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G375" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G378" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G379" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G380" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G381" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992635726929</v>
+        <v>1.71992647647858</v>
       </c>
       <c r="H588" t="n">
         <v>9100</v>
@@ -17450,7 +17450,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H589" t="n">
         <v>18340</v>
@@ -17479,7 +17479,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H590" t="n">
         <v>10566</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H592" t="n">
         <v>4380</v>
@@ -17566,7 +17566,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072888374329</v>
+        <v>1.71072900295258</v>
       </c>
       <c r="H593" t="n">
         <v>3000</v>
@@ -17595,7 +17595,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153152942657</v>
+        <v>1.70153141021729</v>
       </c>
       <c r="H594" t="n">
         <v>7533</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H596" t="n">
         <v>15693</v>
@@ -17740,7 +17740,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554404258728</v>
+        <v>1.65554416179657</v>
       </c>
       <c r="H599" t="n">
         <v>4008</v>
@@ -17769,7 +17769,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H601" t="n">
         <v>9280</v>
@@ -17827,7 +17827,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H602" t="n">
         <v>17225</v>
@@ -17914,7 +17914,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H605" t="n">
         <v>16118</v>
@@ -18030,7 +18030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576070308685</v>
+        <v>1.59576058387756</v>
       </c>
       <c r="H609" t="n">
         <v>91019</v>
@@ -18088,7 +18088,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H611" t="n">
         <v>98468</v>
@@ -18117,7 +18117,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H612" t="n">
         <v>22288</v>
@@ -18146,7 +18146,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H613" t="n">
         <v>43946</v>
@@ -18175,7 +18175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H614" t="n">
         <v>28101</v>
@@ -18204,7 +18204,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H615" t="n">
         <v>25297</v>
@@ -18233,7 +18233,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H616" t="n">
         <v>968</v>
@@ -18262,7 +18262,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H617" t="n">
         <v>150</v>
@@ -18320,7 +18320,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H619" t="n">
         <v>1200</v>
@@ -18407,7 +18407,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H622" t="n">
         <v>12894</v>
@@ -18436,7 +18436,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H623" t="n">
         <v>20448</v>
@@ -18494,7 +18494,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H625" t="n">
         <v>1672</v>
@@ -18610,7 +18610,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421893119812</v>
+        <v>1.38421881198883</v>
       </c>
       <c r="H629" t="n">
         <v>2550</v>
@@ -18639,7 +18639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H630" t="n">
         <v>20080</v>
@@ -18697,7 +18697,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H632" t="n">
         <v>4000</v>
@@ -18813,7 +18813,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H636" t="n">
         <v>23082</v>
@@ -18842,7 +18842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H637" t="n">
         <v>26688</v>
@@ -18929,7 +18929,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714921474457</v>
+        <v>1.63714909553528</v>
       </c>
       <c r="H640" t="n">
         <v>4804</v>
@@ -18958,7 +18958,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H641" t="n">
         <v>41120</v>
@@ -19016,7 +19016,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H643" t="n">
         <v>15100</v>
@@ -19074,7 +19074,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H645" t="n">
         <v>111562</v>
@@ -19103,7 +19103,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H646" t="n">
         <v>16300</v>
@@ -19161,7 +19161,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H648" t="n">
         <v>4602</v>
@@ -19190,7 +19190,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H649" t="n">
         <v>30369</v>
@@ -19277,7 +19277,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H652" t="n">
         <v>100565</v>
@@ -19741,7 +19741,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H668" t="n">
         <v>200</v>
@@ -20060,7 +20060,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H679" t="n">
         <v>31887</v>
@@ -20089,7 +20089,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H680" t="n">
         <v>27161</v>
@@ -20176,7 +20176,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H683" t="n">
         <v>3002</v>
@@ -20205,7 +20205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H686" t="n">
         <v>1802</v>
@@ -20292,7 +20292,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H687" t="n">
         <v>10888</v>
@@ -20408,7 +20408,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H691" t="n">
         <v>9583</v>
@@ -20553,7 +20553,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582386493683</v>
+        <v>1.36582398414612</v>
       </c>
       <c r="H696" t="n">
         <v>32055</v>
@@ -20698,7 +20698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662639141083</v>
+        <v>1.35662651062012</v>
       </c>
       <c r="H701" t="n">
         <v>11820</v>
@@ -20727,7 +20727,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H702" t="n">
         <v>1998</v>
@@ -20756,7 +20756,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H703" t="n">
         <v>350</v>
@@ -20785,7 +20785,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H710" t="n">
         <v>1020</v>
@@ -21075,7 +21075,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H714" t="n">
         <v>10966</v>
@@ -21104,7 +21104,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H717" t="n">
         <v>27660</v>
@@ -21249,7 +21249,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H720" t="n">
         <v>2970</v>
@@ -21278,7 +21278,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H721" t="n">
         <v>1755</v>
@@ -21307,7 +21307,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H722" t="n">
         <v>1321</v>
@@ -21336,7 +21336,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H723" t="n">
         <v>4341</v>
@@ -21423,7 +21423,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H726" t="n">
         <v>6092</v>
@@ -21452,7 +21452,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H727" t="n">
         <v>14923</v>
@@ -21510,7 +21510,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H729" t="n">
         <v>4020</v>
@@ -21597,7 +21597,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H732" t="n">
         <v>8383</v>
@@ -21655,7 +21655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H734" t="n">
         <v>7575</v>
@@ -21887,7 +21887,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H742" t="n">
         <v>9642</v>
@@ -21945,7 +21945,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H744" t="n">
         <v>1128</v>
@@ -22003,7 +22003,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H746" t="n">
         <v>20561</v>
@@ -22061,7 +22061,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H748" t="n">
         <v>302</v>
@@ -22119,7 +22119,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H750" t="n">
         <v>19467</v>
@@ -22148,7 +22148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H751" t="n">
         <v>2586</v>
@@ -22177,7 +22177,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H752" t="n">
         <v>36041</v>
@@ -22206,7 +22206,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H753" t="n">
         <v>10446</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H754" t="n">
         <v>158370</v>
@@ -36857,6 +36857,35 @@
         <v>2768</v>
       </c>
       <c r="I1258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1259" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>12668</v>
+      </c>
+      <c r="I1259" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749710083008</v>
+        <v>2.22749733924866</v>
       </c>
       <c r="H4" t="n">
         <v>60317</v>
@@ -572,7 +572,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2231297492981</v>
+        <v>2.22312951087952</v>
       </c>
       <c r="H7" t="n">
         <v>31322</v>
@@ -601,7 +601,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818879127502</v>
+        <v>2.18818855285645</v>
       </c>
       <c r="H8" t="n">
         <v>38845</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H9" t="n">
         <v>39782</v>
@@ -717,7 +717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H12" t="n">
         <v>21519</v>
@@ -746,7 +746,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H13" t="n">
         <v>3783</v>
@@ -775,7 +775,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04405641555786</v>
+        <v>2.0440559387207</v>
       </c>
       <c r="H14" t="n">
         <v>4196</v>
@@ -862,7 +862,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H17" t="n">
         <v>65997</v>
@@ -920,7 +920,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H19" t="n">
         <v>10225</v>
@@ -949,7 +949,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G20" t="n">
-        <v>2.07899761199951</v>
+        <v>2.07899737358093</v>
       </c>
       <c r="H20" t="n">
         <v>38604</v>
@@ -978,7 +978,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H21" t="n">
         <v>6307</v>
@@ -1007,7 +1007,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H22" t="n">
         <v>64202</v>
@@ -1036,7 +1036,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H23" t="n">
         <v>9285</v>
@@ -1094,7 +1094,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H25" t="n">
         <v>22357</v>
@@ -1152,7 +1152,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532075881958</v>
+        <v>2.03532099723816</v>
       </c>
       <c r="H27" t="n">
         <v>18554</v>
@@ -1181,7 +1181,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H28" t="n">
         <v>33355</v>
@@ -1210,7 +1210,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360029697418</v>
       </c>
       <c r="H29" t="n">
         <v>7100</v>
@@ -1297,7 +1297,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486535549164</v>
+        <v>1.93486523628235</v>
       </c>
       <c r="H32" t="n">
         <v>5405</v>
@@ -1384,7 +1384,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H35" t="n">
         <v>551</v>
@@ -1413,7 +1413,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G36" t="n">
-        <v>1.88245356082916</v>
+        <v>1.88245368003845</v>
       </c>
       <c r="H36" t="n">
         <v>10145</v>
@@ -1442,7 +1442,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8475124835968</v>
+        <v>1.84751236438751</v>
       </c>
       <c r="H37" t="n">
         <v>6948</v>
@@ -1471,7 +1471,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H38" t="n">
         <v>17244</v>
@@ -1558,7 +1558,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532075881958</v>
+        <v>2.03532099723816</v>
       </c>
       <c r="H41" t="n">
         <v>4717</v>
@@ -1645,7 +1645,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.99164462089539</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H44" t="n">
         <v>4404</v>
@@ -1674,7 +1674,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92612981796265</v>
+        <v>1.92612993717194</v>
       </c>
       <c r="H45" t="n">
         <v>842</v>
@@ -1703,7 +1703,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360029697418</v>
       </c>
       <c r="H46" t="n">
         <v>21305</v>
@@ -1761,7 +1761,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H48" t="n">
         <v>72728</v>
@@ -1790,7 +1790,7 @@
         <v>2.5</v>
       </c>
       <c r="G49" t="n">
-        <v>2.18382096290588</v>
+        <v>2.1838207244873</v>
       </c>
       <c r="H49" t="n">
         <v>114387</v>
@@ -1877,7 +1877,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G52" t="n">
-        <v>2.12704110145569</v>
+        <v>2.12704133987427</v>
       </c>
       <c r="H52" t="n">
         <v>44983</v>
@@ -1906,7 +1906,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H53" t="n">
         <v>7775</v>
@@ -1935,7 +1935,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H54" t="n">
         <v>23493</v>
@@ -2022,7 +2022,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176234722137</v>
+        <v>1.92176222801208</v>
       </c>
       <c r="H57" t="n">
         <v>12475</v>
@@ -2051,7 +2051,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G58" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H58" t="n">
         <v>59820</v>
@@ -2138,7 +2138,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H61" t="n">
         <v>15420</v>
@@ -2167,7 +2167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2225,7 +2225,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H64" t="n">
         <v>27250</v>
@@ -2254,7 +2254,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.99164462089539</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H65" t="n">
         <v>62307</v>
@@ -2341,7 +2341,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>2.13140940666199</v>
+        <v>2.13140916824341</v>
       </c>
       <c r="H68" t="n">
         <v>48909</v>
@@ -2370,7 +2370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H69" t="n">
         <v>10560</v>
@@ -2399,7 +2399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H70" t="n">
         <v>2080</v>
@@ -2486,7 +2486,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G73" t="n">
-        <v>2.07899761199951</v>
+        <v>2.07899737358093</v>
       </c>
       <c r="H73" t="n">
         <v>4627</v>
@@ -2515,7 +2515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.99164462089539</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H74" t="n">
         <v>72717</v>
@@ -2602,7 +2602,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G77" t="n">
-        <v>2.13140940666199</v>
+        <v>2.13140916824341</v>
       </c>
       <c r="H77" t="n">
         <v>43135</v>
@@ -2689,7 +2689,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H80" t="n">
         <v>3341</v>
@@ -2747,7 +2747,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G82" t="n">
-        <v>2.07899761199951</v>
+        <v>2.07899737358093</v>
       </c>
       <c r="H82" t="n">
         <v>4785</v>
@@ -2776,7 +2776,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>2.0222179889679</v>
+        <v>2.02221822738647</v>
       </c>
       <c r="H83" t="n">
         <v>2250</v>
@@ -2805,7 +2805,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G84" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H84" t="n">
         <v>40084</v>
@@ -2834,7 +2834,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G85" t="n">
-        <v>1.80383598804474</v>
+        <v>1.80383610725403</v>
       </c>
       <c r="H85" t="n">
         <v>50746</v>
@@ -2863,7 +2863,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371802330017</v>
+        <v>1.87371814250946</v>
       </c>
       <c r="H86" t="n">
         <v>7811</v>
@@ -2921,7 +2921,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H88" t="n">
         <v>42972</v>
@@ -2950,7 +2950,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G89" t="n">
-        <v>1.91739451885223</v>
+        <v>1.91739463806152</v>
       </c>
       <c r="H89" t="n">
         <v>26018</v>
@@ -3008,7 +3008,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G91" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H91" t="n">
         <v>67557</v>
@@ -3066,7 +3066,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H93" t="n">
         <v>27514</v>
@@ -3153,7 +3153,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H96" t="n">
         <v>18344</v>
@@ -3211,7 +3211,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H98" t="n">
         <v>35330</v>
@@ -3269,7 +3269,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.83877718448639</v>
+        <v>1.8387770652771</v>
       </c>
       <c r="H100" t="n">
         <v>42528</v>
@@ -3298,7 +3298,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H101" t="n">
         <v>278213</v>
@@ -3356,7 +3356,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G103" t="n">
-        <v>1.82130646705627</v>
+        <v>1.82130658626556</v>
       </c>
       <c r="H103" t="n">
         <v>23656</v>
@@ -3385,7 +3385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.9392329454422</v>
+        <v>1.93923282623291</v>
       </c>
       <c r="H104" t="n">
         <v>63970</v>
@@ -3414,7 +3414,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.93049764633179</v>
+        <v>1.9304975271225</v>
       </c>
       <c r="H105" t="n">
         <v>93326</v>
@@ -3443,7 +3443,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G106" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H106" t="n">
         <v>43370</v>
@@ -3472,7 +3472,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H107" t="n">
         <v>7685</v>
@@ -3559,7 +3559,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H110" t="n">
         <v>3088</v>
@@ -3588,7 +3588,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G111" t="n">
-        <v>1.88245356082916</v>
+        <v>1.88245368003845</v>
       </c>
       <c r="H111" t="n">
         <v>3762</v>
@@ -3617,7 +3617,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G112" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H112" t="n">
         <v>60471</v>
@@ -3646,7 +3646,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>1.82130646705627</v>
+        <v>1.82130658626556</v>
       </c>
       <c r="H113" t="n">
         <v>4748</v>
@@ -3704,7 +3704,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H115" t="n">
         <v>9850</v>
@@ -3733,7 +3733,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G116" t="n">
-        <v>1.87808609008789</v>
+        <v>1.8780859708786</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.82130646705627</v>
+        <v>1.82130658626556</v>
       </c>
       <c r="H117" t="n">
         <v>3428</v>
@@ -3849,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H120" t="n">
         <v>8950</v>
@@ -3878,7 +3878,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G121" t="n">
-        <v>1.82130646705627</v>
+        <v>1.82130658626556</v>
       </c>
       <c r="H121" t="n">
         <v>66730</v>
@@ -3907,7 +3907,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H122" t="n">
         <v>16909</v>
@@ -3965,7 +3965,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H124" t="n">
         <v>297933</v>
@@ -3994,7 +3994,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H125" t="n">
         <v>101033</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302716732025</v>
+        <v>1.91302692890167</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H127" t="n">
         <v>13630</v>
@@ -4081,7 +4081,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G128" t="n">
-        <v>1.82130646705627</v>
+        <v>1.82130658626556</v>
       </c>
       <c r="H128" t="n">
         <v>2764</v>
@@ -4110,7 +4110,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>1.82130646705627</v>
+        <v>1.82130658626556</v>
       </c>
       <c r="H129" t="n">
         <v>4350</v>
@@ -4168,7 +4168,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H131" t="n">
         <v>7054</v>
@@ -4226,7 +4226,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G133" t="n">
-        <v>1.82130646705627</v>
+        <v>1.82130658626556</v>
       </c>
       <c r="H133" t="n">
         <v>35730</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314453601837</v>
+        <v>1.84314477443695</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4342,7 +4342,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H137" t="n">
         <v>1563</v>
@@ -4371,7 +4371,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H138" t="n">
         <v>3100</v>
@@ -4603,7 +4603,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H146" t="n">
         <v>4619</v>
@@ -4632,7 +4632,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H147" t="n">
         <v>3822</v>
@@ -4719,7 +4719,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H150" t="n">
         <v>43320</v>
@@ -4864,7 +4864,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G155" t="n">
-        <v>1.48849213123322</v>
+        <v>1.4884922504425</v>
       </c>
       <c r="H155" t="n">
         <v>15100</v>
@@ -4922,7 +4922,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235097885132</v>
+        <v>1.57235085964203</v>
       </c>
       <c r="H157" t="n">
         <v>46024</v>
@@ -5125,7 +5125,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.63699197769165</v>
+        <v>1.63699209690094</v>
       </c>
       <c r="H164" t="n">
         <v>10490</v>
@@ -5154,7 +5154,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602735519409</v>
+        <v>1.61602747440338</v>
       </c>
       <c r="H165" t="n">
         <v>10225</v>
@@ -5328,7 +5328,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H171" t="n">
         <v>25750</v>
@@ -5386,7 +5386,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004188537598</v>
+        <v>1.83004176616669</v>
       </c>
       <c r="H173" t="n">
         <v>9852</v>
@@ -5415,7 +5415,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H174" t="n">
         <v>1450</v>
@@ -5444,7 +5444,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H175" t="n">
         <v>5050</v>
@@ -5502,7 +5502,7 @@
         <v>2.06500005722046</v>
       </c>
       <c r="G177" t="n">
-        <v>1.80383598804474</v>
+        <v>1.80383610725403</v>
       </c>
       <c r="H177" t="n">
         <v>3406</v>
@@ -5531,7 +5531,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H178" t="n">
         <v>14700</v>
@@ -5560,7 +5560,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H179" t="n">
         <v>1733</v>
@@ -5589,7 +5589,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015973091125</v>
+        <v>1.76015961170197</v>
       </c>
       <c r="H180" t="n">
         <v>15133</v>
@@ -5618,7 +5618,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H181" t="n">
         <v>1000</v>
@@ -5676,7 +5676,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H183" t="n">
         <v>8218</v>
@@ -5705,7 +5705,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G184" t="n">
-        <v>1.78199768066406</v>
+        <v>1.78199779987335</v>
       </c>
       <c r="H184" t="n">
         <v>289</v>
@@ -5734,7 +5734,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G185" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H185" t="n">
         <v>3794</v>
@@ -5763,7 +5763,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G186" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G187" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G188" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G189" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G190" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G191" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G192" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G193" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G194" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G195" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G196" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G197" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G198" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G199" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G200" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G201" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G202" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G203" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G204" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G205" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G206" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G207" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G208" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G209" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G210" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G211" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G212" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G213" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G214" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G215" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G216" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G217" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G218" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G219" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G220" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G221" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G223" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G224" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G225" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G226" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G227" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G228" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G229" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G230" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G231" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G232" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G233" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G234" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G235" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G236" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G237" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G238" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G239" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G240" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G241" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G242" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G243" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G244" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G245" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G246" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G247" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G248" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G249" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G250" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G251" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G252" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G253" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G254" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G255" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G256" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G257" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G258" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G259" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G260" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G261" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G262" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G263" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G264" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G265" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G266" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G267" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G268" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G269" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G270" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G271" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G272" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G273" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G274" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G275" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G276" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G277" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G278" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G279" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G280" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G281" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G282" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G283" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G284" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G285" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -8663,7 +8663,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G286" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G287" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G288" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G289" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G290" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G291" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G292" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -8866,7 +8866,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G293" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G294" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -8924,7 +8924,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G295" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G296" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -8982,7 +8982,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G298" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G299" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G300" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -9098,7 +9098,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G301" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G302" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G303" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G304" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H304" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G305" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -9243,7 +9243,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G306" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G307" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G308" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G309" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -9359,7 +9359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G310" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -9388,7 +9388,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G311" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G312" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G313" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G314" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G315" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G316" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G317" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -9591,7 +9591,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G318" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G319" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G320" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G322" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -9736,7 +9736,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G323" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -9765,7 +9765,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G324" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -9794,7 +9794,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G325" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -9823,7 +9823,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G326" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G327" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G328" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G329" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -9939,7 +9939,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G330" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -9968,7 +9968,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G331" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G332" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -10026,7 +10026,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G333" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10055,7 +10055,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G334" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -10084,7 +10084,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G335" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -10113,7 +10113,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G336" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G337" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G338" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G339" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G340" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G341" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -10287,7 +10287,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G342" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G343" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10345,7 +10345,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G344" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G345" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G346" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G347" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G348" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -10490,7 +10490,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G349" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -10519,7 +10519,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -10548,7 +10548,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G351" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -10577,7 +10577,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G352" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G353" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -10635,7 +10635,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G354" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -10664,7 +10664,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G355" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -10722,7 +10722,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G357" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G358" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -10780,7 +10780,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G359" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G360" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G362" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -10896,7 +10896,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G363" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -10925,7 +10925,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G364" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G365" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G366" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G367" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G368" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G369" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -11099,7 +11099,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G370" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G371" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G372" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G373" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -11215,7 +11215,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G374" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G375" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G376" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -11302,7 +11302,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G377" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -11331,7 +11331,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G378" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G379" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G380" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G381" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992647647858</v>
+        <v>1.71992635726929</v>
       </c>
       <c r="H588" t="n">
         <v>9100</v>
@@ -17450,7 +17450,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H589" t="n">
         <v>18340</v>
@@ -17479,7 +17479,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H590" t="n">
         <v>10566</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H592" t="n">
         <v>4380</v>
@@ -17566,7 +17566,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072900295258</v>
+        <v>1.71072888374329</v>
       </c>
       <c r="H593" t="n">
         <v>3000</v>
@@ -17595,7 +17595,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153141021729</v>
+        <v>1.70153152942657</v>
       </c>
       <c r="H594" t="n">
         <v>7533</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H596" t="n">
         <v>15693</v>
@@ -17740,7 +17740,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554416179657</v>
+        <v>1.65554404258728</v>
       </c>
       <c r="H599" t="n">
         <v>4008</v>
@@ -17769,7 +17769,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H601" t="n">
         <v>9280</v>
@@ -17827,7 +17827,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736575603485</v>
+        <v>1.57736563682556</v>
       </c>
       <c r="H602" t="n">
         <v>17225</v>
@@ -17914,7 +17914,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H605" t="n">
         <v>16118</v>
@@ -18030,7 +18030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576058387756</v>
+        <v>1.59576070308685</v>
       </c>
       <c r="H609" t="n">
         <v>91019</v>
@@ -18088,7 +18088,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H611" t="n">
         <v>98468</v>
@@ -18117,7 +18117,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918723106384</v>
+        <v>1.49918711185455</v>
       </c>
       <c r="H612" t="n">
         <v>22288</v>
@@ -18146,7 +18146,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H613" t="n">
         <v>43946</v>
@@ -18175,7 +18175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H614" t="n">
         <v>28101</v>
@@ -18204,7 +18204,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H615" t="n">
         <v>25297</v>
@@ -18233,7 +18233,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918723106384</v>
+        <v>1.49918711185455</v>
       </c>
       <c r="H616" t="n">
         <v>968</v>
@@ -18262,7 +18262,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H617" t="n">
         <v>150</v>
@@ -18320,7 +18320,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H619" t="n">
         <v>1200</v>
@@ -18407,7 +18407,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H622" t="n">
         <v>12894</v>
@@ -18436,7 +18436,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H623" t="n">
         <v>20448</v>
@@ -18494,7 +18494,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H625" t="n">
         <v>1672</v>
@@ -18610,7 +18610,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421881198883</v>
+        <v>1.38421893119812</v>
       </c>
       <c r="H629" t="n">
         <v>2550</v>
@@ -18639,7 +18639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H630" t="n">
         <v>20080</v>
@@ -18697,7 +18697,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H632" t="n">
         <v>4000</v>
@@ -18813,7 +18813,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H636" t="n">
         <v>23082</v>
@@ -18842,7 +18842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736575603485</v>
+        <v>1.57736563682556</v>
       </c>
       <c r="H637" t="n">
         <v>26688</v>
@@ -18929,7 +18929,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714909553528</v>
+        <v>1.63714921474457</v>
       </c>
       <c r="H640" t="n">
         <v>4804</v>
@@ -18958,7 +18958,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H641" t="n">
         <v>41120</v>
@@ -19016,7 +19016,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H643" t="n">
         <v>15100</v>
@@ -19074,7 +19074,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H645" t="n">
         <v>111562</v>
@@ -19103,7 +19103,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H646" t="n">
         <v>16300</v>
@@ -19161,7 +19161,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H648" t="n">
         <v>4602</v>
@@ -19190,7 +19190,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H649" t="n">
         <v>30369</v>
@@ -19277,7 +19277,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H652" t="n">
         <v>100565</v>
@@ -19741,7 +19741,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H668" t="n">
         <v>200</v>
@@ -20060,7 +20060,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H679" t="n">
         <v>31887</v>
@@ -20089,7 +20089,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H680" t="n">
         <v>27161</v>
@@ -20176,7 +20176,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H683" t="n">
         <v>3002</v>
@@ -20205,7 +20205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H686" t="n">
         <v>1802</v>
@@ -20292,7 +20292,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H687" t="n">
         <v>10888</v>
@@ -20408,7 +20408,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H691" t="n">
         <v>9583</v>
@@ -20553,7 +20553,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582398414612</v>
+        <v>1.36582386493683</v>
       </c>
       <c r="H696" t="n">
         <v>32055</v>
@@ -20698,7 +20698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662651062012</v>
+        <v>1.35662639141083</v>
       </c>
       <c r="H701" t="n">
         <v>11820</v>
@@ -20727,7 +20727,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H702" t="n">
         <v>1998</v>
@@ -20756,7 +20756,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H703" t="n">
         <v>350</v>
@@ -20785,7 +20785,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H710" t="n">
         <v>1020</v>
@@ -21075,7 +21075,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H714" t="n">
         <v>10966</v>
@@ -21104,7 +21104,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H717" t="n">
         <v>27660</v>
@@ -21249,7 +21249,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H720" t="n">
         <v>2970</v>
@@ -21278,7 +21278,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H721" t="n">
         <v>1755</v>
@@ -21307,7 +21307,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H722" t="n">
         <v>1321</v>
@@ -21336,7 +21336,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H723" t="n">
         <v>4341</v>
@@ -21423,7 +21423,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H726" t="n">
         <v>6092</v>
@@ -21452,7 +21452,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H727" t="n">
         <v>14923</v>
@@ -21510,7 +21510,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H729" t="n">
         <v>4020</v>
@@ -21597,7 +21597,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H732" t="n">
         <v>8383</v>
@@ -21655,7 +21655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H734" t="n">
         <v>7575</v>
@@ -21887,7 +21887,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H742" t="n">
         <v>9642</v>
@@ -21945,7 +21945,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H744" t="n">
         <v>1128</v>
@@ -22003,7 +22003,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H746" t="n">
         <v>20561</v>
@@ -22061,7 +22061,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H748" t="n">
         <v>302</v>
@@ -22119,7 +22119,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H750" t="n">
         <v>19467</v>
@@ -22148,7 +22148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H751" t="n">
         <v>2586</v>
@@ -22177,7 +22177,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H752" t="n">
         <v>36041</v>
@@ -22206,7 +22206,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H753" t="n">
         <v>10446</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H754" t="n">
         <v>158370</v>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668828010559</v>
+        <v>2.33668804168701</v>
       </c>
       <c r="H3" t="n">
         <v>191052</v>
@@ -485,7 +485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749733924866</v>
+        <v>2.22749710083008</v>
       </c>
       <c r="H4" t="n">
         <v>60317</v>
@@ -601,7 +601,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818855285645</v>
+        <v>2.18818831443787</v>
       </c>
       <c r="H8" t="n">
         <v>38845</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H9" t="n">
         <v>39782</v>
@@ -659,7 +659,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H10" t="n">
         <v>12537</v>
@@ -717,7 +717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H12" t="n">
         <v>21519</v>
@@ -775,7 +775,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0440559387207</v>
+        <v>2.04405617713928</v>
       </c>
       <c r="H14" t="n">
         <v>4196</v>
@@ -833,7 +833,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H16" t="n">
         <v>212467</v>
@@ -1036,7 +1036,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H23" t="n">
         <v>9285</v>
@@ -1065,7 +1065,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H24" t="n">
         <v>3610</v>
@@ -1152,7 +1152,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H27" t="n">
         <v>18554</v>
@@ -1210,7 +1210,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H29" t="n">
         <v>7100</v>
@@ -1297,7 +1297,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486523628235</v>
+        <v>1.93486499786377</v>
       </c>
       <c r="H32" t="n">
         <v>5405</v>
@@ -1326,7 +1326,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H33" t="n">
         <v>3600</v>
@@ -1355,7 +1355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H34" t="n">
         <v>17765</v>
@@ -1558,7 +1558,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H41" t="n">
         <v>4717</v>
@@ -1703,7 +1703,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H46" t="n">
         <v>21305</v>
@@ -1848,7 +1848,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761494636536</v>
+        <v>2.15761470794678</v>
       </c>
       <c r="H51" t="n">
         <v>20555</v>
@@ -2022,7 +2022,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176222801208</v>
+        <v>1.92176246643066</v>
       </c>
       <c r="H57" t="n">
         <v>12475</v>
@@ -2080,7 +2080,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H59" t="n">
         <v>31353</v>
@@ -2109,7 +2109,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555644989014</v>
+        <v>1.89555656909943</v>
       </c>
       <c r="H60" t="n">
         <v>26975</v>
@@ -2138,7 +2138,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H61" t="n">
         <v>15420</v>
@@ -2167,7 +2167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2225,7 +2225,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H64" t="n">
         <v>27250</v>
@@ -2312,7 +2312,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026195526123</v>
+        <v>2.07026219367981</v>
       </c>
       <c r="H67" t="n">
         <v>164735</v>
@@ -2370,7 +2370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H69" t="n">
         <v>10560</v>
@@ -2399,7 +2399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H70" t="n">
         <v>2080</v>
@@ -2544,7 +2544,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H75" t="n">
         <v>24848</v>
@@ -2689,7 +2689,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H80" t="n">
         <v>3341</v>
@@ -2863,7 +2863,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371814250946</v>
+        <v>1.87371826171875</v>
       </c>
       <c r="H86" t="n">
         <v>7811</v>
@@ -3269,7 +3269,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.8387770652771</v>
+        <v>1.83877718448639</v>
       </c>
       <c r="H100" t="n">
         <v>42528</v>
@@ -3385,7 +3385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923282623291</v>
+        <v>1.93923306465149</v>
       </c>
       <c r="H104" t="n">
         <v>63970</v>
@@ -3559,7 +3559,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H110" t="n">
         <v>3088</v>
@@ -3907,7 +3907,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H122" t="n">
         <v>16909</v>
@@ -3994,7 +3994,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H125" t="n">
         <v>101033</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302692890167</v>
+        <v>1.91302716732025</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H127" t="n">
         <v>13630</v>
@@ -4168,7 +4168,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H131" t="n">
         <v>7054</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314477443695</v>
+        <v>1.84314453601837</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4342,7 +4342,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H137" t="n">
         <v>1563</v>
@@ -4632,7 +4632,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H147" t="n">
         <v>3822</v>
@@ -4806,7 +4806,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H153" t="n">
         <v>138668</v>
@@ -4835,7 +4835,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.55488038063049</v>
+        <v>1.5548802614212</v>
       </c>
       <c r="H154" t="n">
         <v>63112</v>
@@ -4893,7 +4893,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G156" t="n">
-        <v>1.6247626543045</v>
+        <v>1.62476277351379</v>
       </c>
       <c r="H156" t="n">
         <v>7318</v>
@@ -4922,7 +4922,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235085964203</v>
+        <v>1.57235097885132</v>
       </c>
       <c r="H157" t="n">
         <v>46024</v>
@@ -5038,7 +5038,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H161" t="n">
         <v>13350</v>
@@ -5154,7 +5154,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602747440338</v>
+        <v>1.61602735519409</v>
       </c>
       <c r="H165" t="n">
         <v>10225</v>
@@ -5212,7 +5212,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843903064728</v>
+        <v>1.66843891143799</v>
       </c>
       <c r="H167" t="n">
         <v>51514</v>
@@ -5444,7 +5444,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H175" t="n">
         <v>5050</v>
@@ -5531,7 +5531,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H178" t="n">
         <v>14700</v>
@@ -5589,7 +5589,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015961170197</v>
+        <v>1.76015973091125</v>
       </c>
       <c r="H180" t="n">
         <v>15133</v>
@@ -5676,7 +5676,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H183" t="n">
         <v>8218</v>
@@ -17421,7 +17421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992635726929</v>
+        <v>1.71992647647858</v>
       </c>
       <c r="H588" t="n">
         <v>9100</v>
@@ -17450,7 +17450,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H589" t="n">
         <v>18340</v>
@@ -17479,7 +17479,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H590" t="n">
         <v>10566</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H592" t="n">
         <v>4380</v>
@@ -17566,7 +17566,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072888374329</v>
+        <v>1.71072900295258</v>
       </c>
       <c r="H593" t="n">
         <v>3000</v>
@@ -17595,7 +17595,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153152942657</v>
+        <v>1.70153141021729</v>
       </c>
       <c r="H594" t="n">
         <v>7533</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H596" t="n">
         <v>15693</v>
@@ -17740,7 +17740,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554404258728</v>
+        <v>1.65554416179657</v>
       </c>
       <c r="H599" t="n">
         <v>4008</v>
@@ -17769,7 +17769,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H601" t="n">
         <v>9280</v>
@@ -17827,7 +17827,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H602" t="n">
         <v>17225</v>
@@ -17914,7 +17914,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H605" t="n">
         <v>16118</v>
@@ -18030,7 +18030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576070308685</v>
+        <v>1.59576058387756</v>
       </c>
       <c r="H609" t="n">
         <v>91019</v>
@@ -18088,7 +18088,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H611" t="n">
         <v>98468</v>
@@ -18117,7 +18117,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H612" t="n">
         <v>22288</v>
@@ -18146,7 +18146,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H613" t="n">
         <v>43946</v>
@@ -18175,7 +18175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H614" t="n">
         <v>28101</v>
@@ -18204,7 +18204,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H615" t="n">
         <v>25297</v>
@@ -18233,7 +18233,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H616" t="n">
         <v>968</v>
@@ -18262,7 +18262,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H617" t="n">
         <v>150</v>
@@ -18320,7 +18320,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H619" t="n">
         <v>1200</v>
@@ -18407,7 +18407,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H622" t="n">
         <v>12894</v>
@@ -18436,7 +18436,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H623" t="n">
         <v>20448</v>
@@ -18494,7 +18494,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H625" t="n">
         <v>1672</v>
@@ -18610,7 +18610,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421893119812</v>
+        <v>1.38421881198883</v>
       </c>
       <c r="H629" t="n">
         <v>2550</v>
@@ -18639,7 +18639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H630" t="n">
         <v>20080</v>
@@ -18697,7 +18697,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H632" t="n">
         <v>4000</v>
@@ -18813,7 +18813,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H636" t="n">
         <v>23082</v>
@@ -18842,7 +18842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H637" t="n">
         <v>26688</v>
@@ -18929,7 +18929,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714921474457</v>
+        <v>1.63714909553528</v>
       </c>
       <c r="H640" t="n">
         <v>4804</v>
@@ -18958,7 +18958,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H641" t="n">
         <v>41120</v>
@@ -19016,7 +19016,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H643" t="n">
         <v>15100</v>
@@ -19074,7 +19074,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H645" t="n">
         <v>111562</v>
@@ -19103,7 +19103,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H646" t="n">
         <v>16300</v>
@@ -19161,7 +19161,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H648" t="n">
         <v>4602</v>
@@ -19190,7 +19190,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H649" t="n">
         <v>30369</v>
@@ -19277,7 +19277,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H652" t="n">
         <v>100565</v>
@@ -19741,7 +19741,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H668" t="n">
         <v>200</v>
@@ -20060,7 +20060,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H679" t="n">
         <v>31887</v>
@@ -20089,7 +20089,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H680" t="n">
         <v>27161</v>
@@ -20176,7 +20176,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H683" t="n">
         <v>3002</v>
@@ -20205,7 +20205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H686" t="n">
         <v>1802</v>
@@ -20292,7 +20292,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H687" t="n">
         <v>10888</v>
@@ -20408,7 +20408,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H691" t="n">
         <v>9583</v>
@@ -20553,7 +20553,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582386493683</v>
+        <v>1.36582398414612</v>
       </c>
       <c r="H696" t="n">
         <v>32055</v>
@@ -20698,7 +20698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662639141083</v>
+        <v>1.35662651062012</v>
       </c>
       <c r="H701" t="n">
         <v>11820</v>
@@ -20727,7 +20727,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H702" t="n">
         <v>1998</v>
@@ -20756,7 +20756,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H703" t="n">
         <v>350</v>
@@ -20785,7 +20785,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H710" t="n">
         <v>1020</v>
@@ -21075,7 +21075,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H714" t="n">
         <v>10966</v>
@@ -21104,7 +21104,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H717" t="n">
         <v>27660</v>
@@ -21249,7 +21249,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H720" t="n">
         <v>2970</v>
@@ -21278,7 +21278,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H721" t="n">
         <v>1755</v>
@@ -21307,7 +21307,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H722" t="n">
         <v>1321</v>
@@ -21336,7 +21336,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H723" t="n">
         <v>4341</v>
@@ -21423,7 +21423,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H726" t="n">
         <v>6092</v>
@@ -21452,7 +21452,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H727" t="n">
         <v>14923</v>
@@ -21510,7 +21510,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H729" t="n">
         <v>4020</v>
@@ -21597,7 +21597,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H732" t="n">
         <v>8383</v>
@@ -21655,7 +21655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H734" t="n">
         <v>7575</v>
@@ -21887,7 +21887,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H742" t="n">
         <v>9642</v>
@@ -21945,7 +21945,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H744" t="n">
         <v>1128</v>
@@ -22003,7 +22003,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H746" t="n">
         <v>20561</v>
@@ -22061,7 +22061,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H748" t="n">
         <v>302</v>
@@ -22119,7 +22119,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H750" t="n">
         <v>19467</v>
@@ -22148,7 +22148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H751" t="n">
         <v>2586</v>
@@ -22177,7 +22177,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H752" t="n">
         <v>36041</v>
@@ -22206,7 +22206,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H753" t="n">
         <v>10446</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H754" t="n">
         <v>158370</v>
@@ -36886,6 +36886,64 @@
         <v>12668</v>
       </c>
       <c r="I1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1260" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1261" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>1.35000002384186</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>1.28999996185303</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>12665</v>
+      </c>
+      <c r="I1261" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668804168701</v>
+        <v>2.33668828010559</v>
       </c>
       <c r="H3" t="n">
         <v>191052</v>
@@ -485,7 +485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749710083008</v>
+        <v>2.22749733924866</v>
       </c>
       <c r="H4" t="n">
         <v>60317</v>
@@ -601,7 +601,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818831443787</v>
+        <v>2.18818855285645</v>
       </c>
       <c r="H8" t="n">
         <v>38845</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H9" t="n">
         <v>39782</v>
@@ -659,7 +659,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0921003818512</v>
+        <v>2.09210014343262</v>
       </c>
       <c r="H10" t="n">
         <v>12537</v>
@@ -717,7 +717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H12" t="n">
         <v>21519</v>
@@ -775,7 +775,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04405617713928</v>
+        <v>2.0440559387207</v>
       </c>
       <c r="H14" t="n">
         <v>4196</v>
@@ -833,7 +833,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H16" t="n">
         <v>212467</v>
@@ -1036,7 +1036,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H23" t="n">
         <v>9285</v>
@@ -1065,7 +1065,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0921003818512</v>
+        <v>2.09210014343262</v>
       </c>
       <c r="H24" t="n">
         <v>3610</v>
@@ -1152,7 +1152,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532075881958</v>
+        <v>2.03532099723816</v>
       </c>
       <c r="H27" t="n">
         <v>18554</v>
@@ -1210,7 +1210,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360053539276</v>
+        <v>1.94360029697418</v>
       </c>
       <c r="H29" t="n">
         <v>7100</v>
@@ -1297,7 +1297,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486499786377</v>
+        <v>1.93486523628235</v>
       </c>
       <c r="H32" t="n">
         <v>5405</v>
@@ -1326,7 +1326,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H33" t="n">
         <v>3600</v>
@@ -1355,7 +1355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H34" t="n">
         <v>17765</v>
@@ -1558,7 +1558,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532075881958</v>
+        <v>2.03532099723816</v>
       </c>
       <c r="H41" t="n">
         <v>4717</v>
@@ -1703,7 +1703,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360053539276</v>
+        <v>1.94360029697418</v>
       </c>
       <c r="H46" t="n">
         <v>21305</v>
@@ -1848,7 +1848,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761470794678</v>
+        <v>2.15761494636536</v>
       </c>
       <c r="H51" t="n">
         <v>20555</v>
@@ -2022,7 +2022,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176246643066</v>
+        <v>1.92176222801208</v>
       </c>
       <c r="H57" t="n">
         <v>12475</v>
@@ -2080,7 +2080,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H59" t="n">
         <v>31353</v>
@@ -2109,7 +2109,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555656909943</v>
+        <v>1.89555644989014</v>
       </c>
       <c r="H60" t="n">
         <v>26975</v>
@@ -2138,7 +2138,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H61" t="n">
         <v>15420</v>
@@ -2167,7 +2167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2225,7 +2225,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H64" t="n">
         <v>27250</v>
@@ -2312,7 +2312,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026219367981</v>
+        <v>2.07026195526123</v>
       </c>
       <c r="H67" t="n">
         <v>164735</v>
@@ -2370,7 +2370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H69" t="n">
         <v>10560</v>
@@ -2399,7 +2399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H70" t="n">
         <v>2080</v>
@@ -2544,7 +2544,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>2.0921003818512</v>
+        <v>2.09210014343262</v>
       </c>
       <c r="H75" t="n">
         <v>24848</v>
@@ -2689,7 +2689,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H80" t="n">
         <v>3341</v>
@@ -2863,7 +2863,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371826171875</v>
+        <v>1.87371814250946</v>
       </c>
       <c r="H86" t="n">
         <v>7811</v>
@@ -3269,7 +3269,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.83877718448639</v>
+        <v>1.8387770652771</v>
       </c>
       <c r="H100" t="n">
         <v>42528</v>
@@ -3385,7 +3385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923306465149</v>
+        <v>1.93923282623291</v>
       </c>
       <c r="H104" t="n">
         <v>63970</v>
@@ -3559,7 +3559,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H110" t="n">
         <v>3088</v>
@@ -3907,7 +3907,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81693875789642</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H122" t="n">
         <v>16909</v>
@@ -3994,7 +3994,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061549186707</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H125" t="n">
         <v>101033</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302716732025</v>
+        <v>1.91302692890167</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H127" t="n">
         <v>13630</v>
@@ -4168,7 +4168,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H131" t="n">
         <v>7054</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314453601837</v>
+        <v>1.84314477443695</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4342,7 +4342,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H137" t="n">
         <v>1563</v>
@@ -4632,7 +4632,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.81693875789642</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H147" t="n">
         <v>3822</v>
@@ -4806,7 +4806,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108615875244</v>
+        <v>1.58108627796173</v>
       </c>
       <c r="H153" t="n">
         <v>138668</v>
@@ -4835,7 +4835,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.5548802614212</v>
+        <v>1.55488038063049</v>
       </c>
       <c r="H154" t="n">
         <v>63112</v>
@@ -4893,7 +4893,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G156" t="n">
-        <v>1.62476277351379</v>
+        <v>1.6247626543045</v>
       </c>
       <c r="H156" t="n">
         <v>7318</v>
@@ -4922,7 +4922,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235097885132</v>
+        <v>1.57235085964203</v>
       </c>
       <c r="H157" t="n">
         <v>46024</v>
@@ -5038,7 +5038,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108615875244</v>
+        <v>1.58108627796173</v>
       </c>
       <c r="H161" t="n">
         <v>13350</v>
@@ -5154,7 +5154,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602735519409</v>
+        <v>1.61602747440338</v>
       </c>
       <c r="H165" t="n">
         <v>10225</v>
@@ -5212,7 +5212,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843891143799</v>
+        <v>1.66843903064728</v>
       </c>
       <c r="H167" t="n">
         <v>51514</v>
@@ -5444,7 +5444,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.81693875789642</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H175" t="n">
         <v>5050</v>
@@ -5531,7 +5531,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.81693875789642</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H178" t="n">
         <v>14700</v>
@@ -5589,7 +5589,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015973091125</v>
+        <v>1.76015961170197</v>
       </c>
       <c r="H180" t="n">
         <v>15133</v>
@@ -5676,7 +5676,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H183" t="n">
         <v>8218</v>
@@ -17421,7 +17421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992647647858</v>
+        <v>1.71992635726929</v>
       </c>
       <c r="H588" t="n">
         <v>9100</v>
@@ -17450,7 +17450,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H589" t="n">
         <v>18340</v>
@@ -17479,7 +17479,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H590" t="n">
         <v>10566</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H592" t="n">
         <v>4380</v>
@@ -17566,7 +17566,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072900295258</v>
+        <v>1.71072888374329</v>
       </c>
       <c r="H593" t="n">
         <v>3000</v>
@@ -17595,7 +17595,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153141021729</v>
+        <v>1.70153152942657</v>
       </c>
       <c r="H594" t="n">
         <v>7533</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H596" t="n">
         <v>15693</v>
@@ -17740,7 +17740,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554416179657</v>
+        <v>1.65554404258728</v>
       </c>
       <c r="H599" t="n">
         <v>4008</v>
@@ -17769,7 +17769,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H601" t="n">
         <v>9280</v>
@@ -17827,7 +17827,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736575603485</v>
+        <v>1.57736563682556</v>
       </c>
       <c r="H602" t="n">
         <v>17225</v>
@@ -17914,7 +17914,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H605" t="n">
         <v>16118</v>
@@ -18030,7 +18030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576058387756</v>
+        <v>1.59576070308685</v>
       </c>
       <c r="H609" t="n">
         <v>91019</v>
@@ -18088,7 +18088,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H611" t="n">
         <v>98468</v>
@@ -18117,7 +18117,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918723106384</v>
+        <v>1.49918711185455</v>
       </c>
       <c r="H612" t="n">
         <v>22288</v>
@@ -18146,7 +18146,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H613" t="n">
         <v>43946</v>
@@ -18175,7 +18175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H614" t="n">
         <v>28101</v>
@@ -18204,7 +18204,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H615" t="n">
         <v>25297</v>
@@ -18233,7 +18233,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918723106384</v>
+        <v>1.49918711185455</v>
       </c>
       <c r="H616" t="n">
         <v>968</v>
@@ -18262,7 +18262,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H617" t="n">
         <v>150</v>
@@ -18320,7 +18320,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H619" t="n">
         <v>1200</v>
@@ -18407,7 +18407,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H622" t="n">
         <v>12894</v>
@@ -18436,7 +18436,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H623" t="n">
         <v>20448</v>
@@ -18494,7 +18494,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H625" t="n">
         <v>1672</v>
@@ -18610,7 +18610,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421881198883</v>
+        <v>1.38421893119812</v>
       </c>
       <c r="H629" t="n">
         <v>2550</v>
@@ -18639,7 +18639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H630" t="n">
         <v>20080</v>
@@ -18697,7 +18697,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H632" t="n">
         <v>4000</v>
@@ -18813,7 +18813,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H636" t="n">
         <v>23082</v>
@@ -18842,7 +18842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736575603485</v>
+        <v>1.57736563682556</v>
       </c>
       <c r="H637" t="n">
         <v>26688</v>
@@ -18929,7 +18929,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714909553528</v>
+        <v>1.63714921474457</v>
       </c>
       <c r="H640" t="n">
         <v>4804</v>
@@ -18958,7 +18958,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H641" t="n">
         <v>41120</v>
@@ -19016,7 +19016,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H643" t="n">
         <v>15100</v>
@@ -19074,7 +19074,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H645" t="n">
         <v>111562</v>
@@ -19103,7 +19103,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H646" t="n">
         <v>16300</v>
@@ -19161,7 +19161,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H648" t="n">
         <v>4602</v>
@@ -19190,7 +19190,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H649" t="n">
         <v>30369</v>
@@ -19277,7 +19277,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H652" t="n">
         <v>100565</v>
@@ -19741,7 +19741,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H668" t="n">
         <v>200</v>
@@ -20060,7 +20060,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H679" t="n">
         <v>31887</v>
@@ -20089,7 +20089,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H680" t="n">
         <v>27161</v>
@@ -20176,7 +20176,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H683" t="n">
         <v>3002</v>
@@ -20205,7 +20205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H686" t="n">
         <v>1802</v>
@@ -20292,7 +20292,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H687" t="n">
         <v>10888</v>
@@ -20408,7 +20408,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H691" t="n">
         <v>9583</v>
@@ -20553,7 +20553,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582398414612</v>
+        <v>1.36582386493683</v>
       </c>
       <c r="H696" t="n">
         <v>32055</v>
@@ -20698,7 +20698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662651062012</v>
+        <v>1.35662639141083</v>
       </c>
       <c r="H701" t="n">
         <v>11820</v>
@@ -20727,7 +20727,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H702" t="n">
         <v>1998</v>
@@ -20756,7 +20756,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H703" t="n">
         <v>350</v>
@@ -20785,7 +20785,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H710" t="n">
         <v>1020</v>
@@ -21075,7 +21075,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H714" t="n">
         <v>10966</v>
@@ -21104,7 +21104,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H717" t="n">
         <v>27660</v>
@@ -21249,7 +21249,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H720" t="n">
         <v>2970</v>
@@ -21278,7 +21278,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H721" t="n">
         <v>1755</v>
@@ -21307,7 +21307,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H722" t="n">
         <v>1321</v>
@@ -21336,7 +21336,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H723" t="n">
         <v>4341</v>
@@ -21423,7 +21423,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H726" t="n">
         <v>6092</v>
@@ -21452,7 +21452,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H727" t="n">
         <v>14923</v>
@@ -21510,7 +21510,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H729" t="n">
         <v>4020</v>
@@ -21597,7 +21597,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H732" t="n">
         <v>8383</v>
@@ -21655,7 +21655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H734" t="n">
         <v>7575</v>
@@ -21887,7 +21887,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H742" t="n">
         <v>9642</v>
@@ -21945,7 +21945,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H744" t="n">
         <v>1128</v>
@@ -22003,7 +22003,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H746" t="n">
         <v>20561</v>
@@ -22061,7 +22061,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H748" t="n">
         <v>302</v>
@@ -22119,7 +22119,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H750" t="n">
         <v>19467</v>
@@ -22148,7 +22148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H751" t="n">
         <v>2586</v>
@@ -22177,7 +22177,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H752" t="n">
         <v>36041</v>
@@ -22206,7 +22206,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H753" t="n">
         <v>10446</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H754" t="n">
         <v>158370</v>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749733924866</v>
+        <v>2.22749710083008</v>
       </c>
       <c r="H4" t="n">
         <v>60317</v>
@@ -543,7 +543,7 @@
         <v>2.52900004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>2.209153175354</v>
+        <v>2.20915341377258</v>
       </c>
       <c r="H6" t="n">
         <v>64688</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H9" t="n">
         <v>39782</v>
@@ -659,7 +659,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H10" t="n">
         <v>12537</v>
@@ -717,7 +717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H12" t="n">
         <v>21519</v>
@@ -746,7 +746,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H13" t="n">
         <v>3783</v>
@@ -775,7 +775,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0440559387207</v>
+        <v>2.04405617713928</v>
       </c>
       <c r="H14" t="n">
         <v>4196</v>
@@ -833,7 +833,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H16" t="n">
         <v>212467</v>
@@ -862,7 +862,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H17" t="n">
         <v>65997</v>
@@ -920,7 +920,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H19" t="n">
         <v>10225</v>
@@ -978,7 +978,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H21" t="n">
         <v>6307</v>
@@ -1007,7 +1007,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267398834229</v>
+        <v>2.12267374992371</v>
       </c>
       <c r="H22" t="n">
         <v>64202</v>
@@ -1036,7 +1036,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H23" t="n">
         <v>9285</v>
@@ -1065,7 +1065,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H24" t="n">
         <v>3610</v>
@@ -1094,7 +1094,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911521911621</v>
+        <v>2.00911498069763</v>
       </c>
       <c r="H25" t="n">
         <v>22357</v>
@@ -1152,7 +1152,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H27" t="n">
         <v>18554</v>
@@ -1181,7 +1181,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H28" t="n">
         <v>33355</v>
@@ -1210,7 +1210,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360041618347</v>
       </c>
       <c r="H29" t="n">
         <v>7100</v>
@@ -1297,7 +1297,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486523628235</v>
+        <v>1.93486511707306</v>
       </c>
       <c r="H32" t="n">
         <v>5405</v>
@@ -1326,7 +1326,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H33" t="n">
         <v>3600</v>
@@ -1355,7 +1355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H34" t="n">
         <v>17765</v>
@@ -1384,7 +1384,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H35" t="n">
         <v>551</v>
@@ -1471,7 +1471,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02658557891846</v>
+        <v>2.02658581733704</v>
       </c>
       <c r="H38" t="n">
         <v>17244</v>
@@ -1558,7 +1558,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H41" t="n">
         <v>4717</v>
@@ -1645,7 +1645,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164438247681</v>
       </c>
       <c r="H44" t="n">
         <v>4404</v>
@@ -1674,7 +1674,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92612993717194</v>
+        <v>1.92613005638123</v>
       </c>
       <c r="H45" t="n">
         <v>842</v>
@@ -1703,7 +1703,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360041618347</v>
       </c>
       <c r="H46" t="n">
         <v>21305</v>
@@ -1761,7 +1761,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267398834229</v>
+        <v>2.12267374992371</v>
       </c>
       <c r="H48" t="n">
         <v>72728</v>
@@ -1906,7 +1906,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152653694153</v>
+        <v>2.06152677536011</v>
       </c>
       <c r="H53" t="n">
         <v>7775</v>
@@ -1935,7 +1935,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911521911621</v>
+        <v>2.00911498069763</v>
       </c>
       <c r="H54" t="n">
         <v>23493</v>
@@ -2022,7 +2022,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176222801208</v>
+        <v>1.92176246643066</v>
       </c>
       <c r="H57" t="n">
         <v>12475</v>
@@ -2080,7 +2080,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H59" t="n">
         <v>31353</v>
@@ -2138,7 +2138,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061561107635</v>
       </c>
       <c r="H61" t="n">
         <v>15420</v>
@@ -2167,7 +2167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2225,7 +2225,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061561107635</v>
       </c>
       <c r="H64" t="n">
         <v>27250</v>
@@ -2254,7 +2254,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164438247681</v>
       </c>
       <c r="H65" t="n">
         <v>62307</v>
@@ -2312,7 +2312,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026195526123</v>
+        <v>2.07026219367981</v>
       </c>
       <c r="H67" t="n">
         <v>164735</v>
@@ -2370,7 +2370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H69" t="n">
         <v>10560</v>
@@ -2399,7 +2399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H70" t="n">
         <v>2080</v>
@@ -2515,7 +2515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.9916445016861</v>
+        <v>1.99164438247681</v>
       </c>
       <c r="H74" t="n">
         <v>72717</v>
@@ -2544,7 +2544,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H75" t="n">
         <v>24848</v>
@@ -2573,7 +2573,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.16635036468506</v>
+        <v>2.16635012626648</v>
       </c>
       <c r="H76" t="n">
         <v>93029</v>
@@ -2689,7 +2689,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H80" t="n">
         <v>3341</v>
@@ -2776,7 +2776,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>2.02221822738647</v>
+        <v>2.0222179889679</v>
       </c>
       <c r="H83" t="n">
         <v>2250</v>
@@ -2921,7 +2921,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H88" t="n">
         <v>42972</v>
@@ -3066,7 +3066,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H93" t="n">
         <v>27514</v>
@@ -3153,7 +3153,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H96" t="n">
         <v>18344</v>
@@ -3211,7 +3211,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H98" t="n">
         <v>35330</v>
@@ -3269,7 +3269,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.8387770652771</v>
+        <v>1.83877730369568</v>
       </c>
       <c r="H100" t="n">
         <v>42528</v>
@@ -3298,7 +3298,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429186820984</v>
+        <v>1.90429198741913</v>
       </c>
       <c r="H101" t="n">
         <v>278213</v>
@@ -3385,7 +3385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923282623291</v>
+        <v>1.9392329454422</v>
       </c>
       <c r="H104" t="n">
         <v>63970</v>
@@ -3414,7 +3414,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.9304975271225</v>
+        <v>1.93049764633179</v>
       </c>
       <c r="H105" t="n">
         <v>93326</v>
@@ -3472,7 +3472,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440947532654</v>
+        <v>1.83440935611725</v>
       </c>
       <c r="H107" t="n">
         <v>7685</v>
@@ -3559,7 +3559,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H110" t="n">
         <v>3088</v>
@@ -3849,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H120" t="n">
         <v>8950</v>
@@ -3907,7 +3907,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H122" t="n">
         <v>16909</v>
@@ -3965,7 +3965,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510080814362</v>
+        <v>1.79510068893433</v>
       </c>
       <c r="H124" t="n">
         <v>297933</v>
@@ -3994,7 +3994,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061561107635</v>
       </c>
       <c r="H125" t="n">
         <v>101033</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302692890167</v>
+        <v>1.91302704811096</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H127" t="n">
         <v>13630</v>
@@ -4168,7 +4168,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H131" t="n">
         <v>7054</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314477443695</v>
+        <v>1.84314453601837</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4342,7 +4342,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H137" t="n">
         <v>1563</v>
@@ -4371,7 +4371,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>1.76452708244324</v>
+        <v>1.76452720165253</v>
       </c>
       <c r="H138" t="n">
         <v>3100</v>
@@ -4632,7 +4632,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H147" t="n">
         <v>3822</v>
@@ -4719,7 +4719,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H150" t="n">
         <v>43320</v>
@@ -4748,7 +4748,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74530959129333</v>
+        <v>1.74530947208405</v>
       </c>
       <c r="H151" t="n">
         <v>20277</v>
@@ -4893,7 +4893,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G156" t="n">
-        <v>1.6247626543045</v>
+        <v>1.62476277351379</v>
       </c>
       <c r="H156" t="n">
         <v>7318</v>
@@ -4922,7 +4922,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235085964203</v>
+        <v>1.57235097885132</v>
       </c>
       <c r="H157" t="n">
         <v>46024</v>
@@ -5125,7 +5125,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.63699209690094</v>
+        <v>1.63699197769165</v>
       </c>
       <c r="H164" t="n">
         <v>10490</v>
@@ -5154,7 +5154,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602747440338</v>
+        <v>1.61602735519409</v>
       </c>
       <c r="H165" t="n">
         <v>10225</v>
@@ -5328,7 +5328,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.74705672264099</v>
+        <v>1.7470566034317</v>
       </c>
       <c r="H171" t="n">
         <v>25750</v>
@@ -5386,7 +5386,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004176616669</v>
+        <v>1.83004188537598</v>
       </c>
       <c r="H173" t="n">
         <v>9852</v>
@@ -5415,7 +5415,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440947532654</v>
+        <v>1.83440935611725</v>
       </c>
       <c r="H174" t="n">
         <v>1450</v>
@@ -5444,7 +5444,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H175" t="n">
         <v>5050</v>
@@ -5531,7 +5531,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693887710571</v>
       </c>
       <c r="H178" t="n">
         <v>14700</v>
@@ -5560,7 +5560,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510080814362</v>
+        <v>1.79510068893433</v>
       </c>
       <c r="H179" t="n">
         <v>1733</v>
@@ -5589,7 +5589,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015961170197</v>
+        <v>1.76015973091125</v>
       </c>
       <c r="H180" t="n">
         <v>15133</v>
@@ -5676,7 +5676,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H183" t="n">
         <v>8218</v>
@@ -17421,7 +17421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992635726929</v>
+        <v>1.71992647647858</v>
       </c>
       <c r="H588" t="n">
         <v>9100</v>
@@ -17450,7 +17450,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H589" t="n">
         <v>18340</v>
@@ -17479,7 +17479,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H590" t="n">
         <v>10566</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H592" t="n">
         <v>4380</v>
@@ -17566,7 +17566,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072888374329</v>
+        <v>1.71072900295258</v>
       </c>
       <c r="H593" t="n">
         <v>3000</v>
@@ -17595,7 +17595,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153152942657</v>
+        <v>1.70153141021729</v>
       </c>
       <c r="H594" t="n">
         <v>7533</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H596" t="n">
         <v>15693</v>
@@ -17740,7 +17740,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554404258728</v>
+        <v>1.65554416179657</v>
       </c>
       <c r="H599" t="n">
         <v>4008</v>
@@ -17769,7 +17769,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H601" t="n">
         <v>9280</v>
@@ -17827,7 +17827,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H602" t="n">
         <v>17225</v>
@@ -17914,7 +17914,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H605" t="n">
         <v>16118</v>
@@ -18030,7 +18030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576070308685</v>
+        <v>1.59576058387756</v>
       </c>
       <c r="H609" t="n">
         <v>91019</v>
@@ -18088,7 +18088,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H611" t="n">
         <v>98468</v>
@@ -18117,7 +18117,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H612" t="n">
         <v>22288</v>
@@ -18146,7 +18146,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H613" t="n">
         <v>43946</v>
@@ -18175,7 +18175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H614" t="n">
         <v>28101</v>
@@ -18204,7 +18204,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H615" t="n">
         <v>25297</v>
@@ -18233,7 +18233,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H616" t="n">
         <v>968</v>
@@ -18262,7 +18262,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H617" t="n">
         <v>150</v>
@@ -18320,7 +18320,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H619" t="n">
         <v>1200</v>
@@ -18407,7 +18407,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H622" t="n">
         <v>12894</v>
@@ -18436,7 +18436,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H623" t="n">
         <v>20448</v>
@@ -18494,7 +18494,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H625" t="n">
         <v>1672</v>
@@ -18610,7 +18610,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421893119812</v>
+        <v>1.38421881198883</v>
       </c>
       <c r="H629" t="n">
         <v>2550</v>
@@ -18639,7 +18639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H630" t="n">
         <v>20080</v>
@@ -18697,7 +18697,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H632" t="n">
         <v>4000</v>
@@ -18813,7 +18813,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H636" t="n">
         <v>23082</v>
@@ -18842,7 +18842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H637" t="n">
         <v>26688</v>
@@ -18929,7 +18929,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714921474457</v>
+        <v>1.63714909553528</v>
       </c>
       <c r="H640" t="n">
         <v>4804</v>
@@ -18958,7 +18958,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H641" t="n">
         <v>41120</v>
@@ -19016,7 +19016,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H643" t="n">
         <v>15100</v>
@@ -19074,7 +19074,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H645" t="n">
         <v>111562</v>
@@ -19103,7 +19103,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H646" t="n">
         <v>16300</v>
@@ -19161,7 +19161,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H648" t="n">
         <v>4602</v>
@@ -19190,7 +19190,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H649" t="n">
         <v>30369</v>
@@ -19277,7 +19277,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H652" t="n">
         <v>100565</v>
@@ -19741,7 +19741,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H668" t="n">
         <v>200</v>
@@ -20060,7 +20060,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H679" t="n">
         <v>31887</v>
@@ -20089,7 +20089,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H680" t="n">
         <v>27161</v>
@@ -20176,7 +20176,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H683" t="n">
         <v>3002</v>
@@ -20205,7 +20205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H686" t="n">
         <v>1802</v>
@@ -20292,7 +20292,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H687" t="n">
         <v>10888</v>
@@ -20408,7 +20408,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H691" t="n">
         <v>9583</v>
@@ -20553,7 +20553,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582386493683</v>
+        <v>1.36582398414612</v>
       </c>
       <c r="H696" t="n">
         <v>32055</v>
@@ -20698,7 +20698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662639141083</v>
+        <v>1.35662651062012</v>
       </c>
       <c r="H701" t="n">
         <v>11820</v>
@@ -20727,7 +20727,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H702" t="n">
         <v>1998</v>
@@ -20756,7 +20756,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H703" t="n">
         <v>350</v>
@@ -20785,7 +20785,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H710" t="n">
         <v>1020</v>
@@ -21075,7 +21075,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H714" t="n">
         <v>10966</v>
@@ -21104,7 +21104,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H717" t="n">
         <v>27660</v>
@@ -21249,7 +21249,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H720" t="n">
         <v>2970</v>
@@ -21278,7 +21278,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H721" t="n">
         <v>1755</v>
@@ -21307,7 +21307,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H722" t="n">
         <v>1321</v>
@@ -21336,7 +21336,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H723" t="n">
         <v>4341</v>
@@ -21423,7 +21423,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H726" t="n">
         <v>6092</v>
@@ -21452,7 +21452,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H727" t="n">
         <v>14923</v>
@@ -21510,7 +21510,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H729" t="n">
         <v>4020</v>
@@ -21597,7 +21597,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H732" t="n">
         <v>8383</v>
@@ -21655,7 +21655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H734" t="n">
         <v>7575</v>
@@ -21887,7 +21887,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H742" t="n">
         <v>9642</v>
@@ -21945,7 +21945,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H744" t="n">
         <v>1128</v>
@@ -22003,7 +22003,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H746" t="n">
         <v>20561</v>
@@ -22061,7 +22061,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H748" t="n">
         <v>302</v>
@@ -22119,7 +22119,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H750" t="n">
         <v>19467</v>
@@ -22148,7 +22148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H751" t="n">
         <v>2586</v>
@@ -22177,7 +22177,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H752" t="n">
         <v>36041</v>
@@ -22206,7 +22206,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H753" t="n">
         <v>10446</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H754" t="n">
         <v>158370</v>
@@ -36944,6 +36944,64 @@
         <v>12665</v>
       </c>
       <c r="I1261" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1262" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1262" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G1262" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H1262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1262" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1263" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1263" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="D1263" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="E1263" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="G1263" t="n">
+        <v>1.27499997615814</v>
+      </c>
+      <c r="H1263" t="n">
+        <v>400</v>
+      </c>
+      <c r="I1263" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749710083008</v>
+        <v>2.22749733924866</v>
       </c>
       <c r="H4" t="n">
         <v>60317</v>
@@ -543,7 +543,7 @@
         <v>2.52900004386902</v>
       </c>
       <c r="G6" t="n">
-        <v>2.20915341377258</v>
+        <v>2.209153175354</v>
       </c>
       <c r="H6" t="n">
         <v>64688</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H9" t="n">
         <v>39782</v>
@@ -659,7 +659,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0921003818512</v>
+        <v>2.09210014343262</v>
       </c>
       <c r="H10" t="n">
         <v>12537</v>
@@ -717,7 +717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H12" t="n">
         <v>21519</v>
@@ -746,7 +746,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H13" t="n">
         <v>3783</v>
@@ -775,7 +775,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04405617713928</v>
+        <v>2.0440559387207</v>
       </c>
       <c r="H14" t="n">
         <v>4196</v>
@@ -833,7 +833,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H16" t="n">
         <v>212467</v>
@@ -862,7 +862,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H17" t="n">
         <v>65997</v>
@@ -920,7 +920,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G19" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H19" t="n">
         <v>10225</v>
@@ -978,7 +978,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H21" t="n">
         <v>6307</v>
@@ -1007,7 +1007,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H22" t="n">
         <v>64202</v>
@@ -1036,7 +1036,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H23" t="n">
         <v>9285</v>
@@ -1065,7 +1065,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0921003818512</v>
+        <v>2.09210014343262</v>
       </c>
       <c r="H24" t="n">
         <v>3610</v>
@@ -1094,7 +1094,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G25" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H25" t="n">
         <v>22357</v>
@@ -1152,7 +1152,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532075881958</v>
+        <v>2.03532099723816</v>
       </c>
       <c r="H27" t="n">
         <v>18554</v>
@@ -1181,7 +1181,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G28" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H28" t="n">
         <v>33355</v>
@@ -1210,7 +1210,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360029697418</v>
       </c>
       <c r="H29" t="n">
         <v>7100</v>
@@ -1297,7 +1297,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486511707306</v>
+        <v>1.93486523628235</v>
       </c>
       <c r="H32" t="n">
         <v>5405</v>
@@ -1326,7 +1326,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H33" t="n">
         <v>3600</v>
@@ -1355,7 +1355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H34" t="n">
         <v>17765</v>
@@ -1384,7 +1384,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G35" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H35" t="n">
         <v>551</v>
@@ -1471,7 +1471,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G38" t="n">
-        <v>2.02658581733704</v>
+        <v>2.02658557891846</v>
       </c>
       <c r="H38" t="n">
         <v>17244</v>
@@ -1558,7 +1558,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532075881958</v>
+        <v>2.03532099723816</v>
       </c>
       <c r="H41" t="n">
         <v>4717</v>
@@ -1645,7 +1645,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G44" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H44" t="n">
         <v>4404</v>
@@ -1674,7 +1674,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>1.92613005638123</v>
+        <v>1.92612993717194</v>
       </c>
       <c r="H45" t="n">
         <v>842</v>
@@ -1703,7 +1703,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360041618347</v>
+        <v>1.94360029697418</v>
       </c>
       <c r="H46" t="n">
         <v>21305</v>
@@ -1761,7 +1761,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G48" t="n">
-        <v>2.12267374992371</v>
+        <v>2.12267398834229</v>
       </c>
       <c r="H48" t="n">
         <v>72728</v>
@@ -1906,7 +1906,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06152677536011</v>
+        <v>2.06152653694153</v>
       </c>
       <c r="H53" t="n">
         <v>7775</v>
@@ -1935,7 +1935,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G54" t="n">
-        <v>2.00911498069763</v>
+        <v>2.00911521911621</v>
       </c>
       <c r="H54" t="n">
         <v>23493</v>
@@ -2022,7 +2022,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176246643066</v>
+        <v>1.92176222801208</v>
       </c>
       <c r="H57" t="n">
         <v>12475</v>
@@ -2080,7 +2080,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.88682115077972</v>
+        <v>1.88682126998901</v>
       </c>
       <c r="H59" t="n">
         <v>31353</v>
@@ -2138,7 +2138,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H61" t="n">
         <v>15420</v>
@@ -2167,7 +2167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2225,7 +2225,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H64" t="n">
         <v>27250</v>
@@ -2254,7 +2254,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G65" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H65" t="n">
         <v>62307</v>
@@ -2312,7 +2312,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026219367981</v>
+        <v>2.07026195526123</v>
       </c>
       <c r="H67" t="n">
         <v>164735</v>
@@ -2370,7 +2370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H69" t="n">
         <v>10560</v>
@@ -2399,7 +2399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646797180176</v>
+        <v>2.09646821022034</v>
       </c>
       <c r="H70" t="n">
         <v>2080</v>
@@ -2515,7 +2515,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G74" t="n">
-        <v>1.99164438247681</v>
+        <v>1.9916445016861</v>
       </c>
       <c r="H74" t="n">
         <v>72717</v>
@@ -2544,7 +2544,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>2.0921003818512</v>
+        <v>2.09210014343262</v>
       </c>
       <c r="H75" t="n">
         <v>24848</v>
@@ -2573,7 +2573,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>2.16635012626648</v>
+        <v>2.16635036468506</v>
       </c>
       <c r="H76" t="n">
         <v>93029</v>
@@ -2689,7 +2689,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393880844116</v>
+        <v>2.11393857002258</v>
       </c>
       <c r="H80" t="n">
         <v>3341</v>
@@ -2776,7 +2776,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G83" t="n">
-        <v>2.0222179889679</v>
+        <v>2.02221822738647</v>
       </c>
       <c r="H83" t="n">
         <v>2250</v>
@@ -2921,7 +2921,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G88" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H88" t="n">
         <v>42972</v>
@@ -3066,7 +3066,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G93" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H93" t="n">
         <v>27514</v>
@@ -3153,7 +3153,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H96" t="n">
         <v>18344</v>
@@ -3211,7 +3211,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G98" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H98" t="n">
         <v>35330</v>
@@ -3269,7 +3269,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.83877730369568</v>
+        <v>1.8387770652771</v>
       </c>
       <c r="H100" t="n">
         <v>42528</v>
@@ -3298,7 +3298,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G101" t="n">
-        <v>1.90429198741913</v>
+        <v>1.90429186820984</v>
       </c>
       <c r="H101" t="n">
         <v>278213</v>
@@ -3385,7 +3385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.9392329454422</v>
+        <v>1.93923282623291</v>
       </c>
       <c r="H104" t="n">
         <v>63970</v>
@@ -3414,7 +3414,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G105" t="n">
-        <v>1.93049764633179</v>
+        <v>1.9304975271225</v>
       </c>
       <c r="H105" t="n">
         <v>93326</v>
@@ -3472,7 +3472,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G107" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H107" t="n">
         <v>7685</v>
@@ -3559,7 +3559,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H110" t="n">
         <v>3088</v>
@@ -3849,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H120" t="n">
         <v>8950</v>
@@ -3907,7 +3907,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H122" t="n">
         <v>16909</v>
@@ -3965,7 +3965,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G124" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H124" t="n">
         <v>297933</v>
@@ -3994,7 +3994,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061561107635</v>
+        <v>1.86061537265778</v>
       </c>
       <c r="H125" t="n">
         <v>101033</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302704811096</v>
+        <v>1.91302692890167</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85187995433807</v>
+        <v>1.85188007354736</v>
       </c>
       <c r="H127" t="n">
         <v>13630</v>
@@ -4168,7 +4168,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H131" t="n">
         <v>7054</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314453601837</v>
+        <v>1.84314477443695</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4342,7 +4342,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H137" t="n">
         <v>1563</v>
@@ -4371,7 +4371,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>1.76452720165253</v>
+        <v>1.76452708244324</v>
       </c>
       <c r="H138" t="n">
         <v>3100</v>
@@ -4632,7 +4632,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H147" t="n">
         <v>3822</v>
@@ -4719,7 +4719,7 @@
         <v>2</v>
       </c>
       <c r="G150" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H150" t="n">
         <v>43320</v>
@@ -4748,7 +4748,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G151" t="n">
-        <v>1.74530947208405</v>
+        <v>1.74530959129333</v>
       </c>
       <c r="H151" t="n">
         <v>20277</v>
@@ -4893,7 +4893,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G156" t="n">
-        <v>1.62476277351379</v>
+        <v>1.6247626543045</v>
       </c>
       <c r="H156" t="n">
         <v>7318</v>
@@ -4922,7 +4922,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235097885132</v>
+        <v>1.57235085964203</v>
       </c>
       <c r="H157" t="n">
         <v>46024</v>
@@ -5125,7 +5125,7 @@
         <v>1.87399995326996</v>
       </c>
       <c r="G164" t="n">
-        <v>1.63699197769165</v>
+        <v>1.63699209690094</v>
       </c>
       <c r="H164" t="n">
         <v>10490</v>
@@ -5154,7 +5154,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602735519409</v>
+        <v>1.61602747440338</v>
       </c>
       <c r="H165" t="n">
         <v>10225</v>
@@ -5328,7 +5328,7 @@
         <v>2</v>
       </c>
       <c r="G171" t="n">
-        <v>1.7470566034317</v>
+        <v>1.74705672264099</v>
       </c>
       <c r="H171" t="n">
         <v>25750</v>
@@ -5386,7 +5386,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G173" t="n">
-        <v>1.83004188537598</v>
+        <v>1.83004176616669</v>
       </c>
       <c r="H173" t="n">
         <v>9852</v>
@@ -5415,7 +5415,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G174" t="n">
-        <v>1.83440935611725</v>
+        <v>1.83440947532654</v>
       </c>
       <c r="H174" t="n">
         <v>1450</v>
@@ -5444,7 +5444,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H175" t="n">
         <v>5050</v>
@@ -5531,7 +5531,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.81693887710571</v>
+        <v>1.816938996315</v>
       </c>
       <c r="H178" t="n">
         <v>14700</v>
@@ -5560,7 +5560,7 @@
         <v>2.0550000667572</v>
       </c>
       <c r="G179" t="n">
-        <v>1.79510068893433</v>
+        <v>1.79510080814362</v>
       </c>
       <c r="H179" t="n">
         <v>1733</v>
@@ -5589,7 +5589,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015973091125</v>
+        <v>1.76015961170197</v>
       </c>
       <c r="H180" t="n">
         <v>15133</v>
@@ -5676,7 +5676,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.7863655090332</v>
+        <v>1.78636562824249</v>
       </c>
       <c r="H183" t="n">
         <v>8218</v>
@@ -17421,7 +17421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992647647858</v>
+        <v>1.71992635726929</v>
       </c>
       <c r="H588" t="n">
         <v>9100</v>
@@ -17450,7 +17450,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H589" t="n">
         <v>18340</v>
@@ -17479,7 +17479,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H590" t="n">
         <v>10566</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832130432129</v>
+        <v>1.73832142353058</v>
       </c>
       <c r="H592" t="n">
         <v>4380</v>
@@ -17566,7 +17566,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072900295258</v>
+        <v>1.71072888374329</v>
       </c>
       <c r="H593" t="n">
         <v>3000</v>
@@ -17595,7 +17595,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153141021729</v>
+        <v>1.70153152942657</v>
       </c>
       <c r="H594" t="n">
         <v>7533</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H596" t="n">
         <v>15693</v>
@@ -17740,7 +17740,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554416179657</v>
+        <v>1.65554404258728</v>
       </c>
       <c r="H599" t="n">
         <v>4008</v>
@@ -17769,7 +17769,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174795150757</v>
+        <v>1.64174783229828</v>
       </c>
       <c r="H601" t="n">
         <v>9280</v>
@@ -17827,7 +17827,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736575603485</v>
+        <v>1.57736563682556</v>
       </c>
       <c r="H602" t="n">
         <v>17225</v>
@@ -17914,7 +17914,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H605" t="n">
         <v>16118</v>
@@ -18030,7 +18030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576058387756</v>
+        <v>1.59576070308685</v>
       </c>
       <c r="H609" t="n">
         <v>91019</v>
@@ -18088,7 +18088,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H611" t="n">
         <v>98468</v>
@@ -18117,7 +18117,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918723106384</v>
+        <v>1.49918711185455</v>
       </c>
       <c r="H612" t="n">
         <v>22288</v>
@@ -18146,7 +18146,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H613" t="n">
         <v>43946</v>
@@ -18175,7 +18175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H614" t="n">
         <v>28101</v>
@@ -18204,7 +18204,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838470458984</v>
+        <v>1.50838458538055</v>
       </c>
       <c r="H615" t="n">
         <v>25297</v>
@@ -18233,7 +18233,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918723106384</v>
+        <v>1.49918711185455</v>
       </c>
       <c r="H616" t="n">
         <v>968</v>
@@ -18262,7 +18262,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H617" t="n">
         <v>150</v>
@@ -18320,7 +18320,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H619" t="n">
         <v>1200</v>
@@ -18407,7 +18407,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H622" t="n">
         <v>12894</v>
@@ -18436,7 +18436,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H623" t="n">
         <v>20448</v>
@@ -18494,7 +18494,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H625" t="n">
         <v>1672</v>
@@ -18610,7 +18610,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421881198883</v>
+        <v>1.38421893119812</v>
       </c>
       <c r="H629" t="n">
         <v>2550</v>
@@ -18639,7 +18639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H630" t="n">
         <v>20080</v>
@@ -18697,7 +18697,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H632" t="n">
         <v>4000</v>
@@ -18813,7 +18813,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H636" t="n">
         <v>23082</v>
@@ -18842,7 +18842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736575603485</v>
+        <v>1.57736563682556</v>
       </c>
       <c r="H637" t="n">
         <v>26688</v>
@@ -18929,7 +18929,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714909553528</v>
+        <v>1.63714921474457</v>
       </c>
       <c r="H640" t="n">
         <v>4804</v>
@@ -18958,7 +18958,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H641" t="n">
         <v>41120</v>
@@ -19016,7 +19016,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H643" t="n">
         <v>15100</v>
@@ -19074,7 +19074,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H645" t="n">
         <v>111562</v>
@@ -19103,7 +19103,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H646" t="n">
         <v>16300</v>
@@ -19161,7 +19161,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H648" t="n">
         <v>4602</v>
@@ -19190,7 +19190,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H649" t="n">
         <v>30369</v>
@@ -19277,7 +19277,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897068977356</v>
+        <v>1.55897080898285</v>
       </c>
       <c r="H652" t="n">
         <v>100565</v>
@@ -19741,7 +19741,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H668" t="n">
         <v>200</v>
@@ -20060,7 +20060,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H679" t="n">
         <v>31887</v>
@@ -20089,7 +20089,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H680" t="n">
         <v>27161</v>
@@ -20176,7 +20176,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H683" t="n">
         <v>3002</v>
@@ -20205,7 +20205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H686" t="n">
         <v>1802</v>
@@ -20292,7 +20292,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H687" t="n">
         <v>10888</v>
@@ -20408,7 +20408,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H691" t="n">
         <v>9583</v>
@@ -20553,7 +20553,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582398414612</v>
+        <v>1.36582386493683</v>
       </c>
       <c r="H696" t="n">
         <v>32055</v>
@@ -20698,7 +20698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662651062012</v>
+        <v>1.35662639141083</v>
       </c>
       <c r="H701" t="n">
         <v>11820</v>
@@ -20727,7 +20727,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H702" t="n">
         <v>1998</v>
@@ -20756,7 +20756,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H703" t="n">
         <v>350</v>
@@ -20785,7 +20785,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881754875183</v>
+        <v>1.38881766796112</v>
       </c>
       <c r="H710" t="n">
         <v>1020</v>
@@ -21075,7 +21075,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H714" t="n">
         <v>10966</v>
@@ -21104,7 +21104,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560732364655</v>
+        <v>1.42560744285583</v>
       </c>
       <c r="H717" t="n">
         <v>27660</v>
@@ -21249,7 +21249,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H720" t="n">
         <v>2970</v>
@@ -21278,7 +21278,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H721" t="n">
         <v>1755</v>
@@ -21307,7 +21307,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H722" t="n">
         <v>1321</v>
@@ -21336,7 +21336,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020617961884</v>
+        <v>1.43020606040955</v>
       </c>
       <c r="H723" t="n">
         <v>4341</v>
@@ -21423,7 +21423,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H726" t="n">
         <v>6092</v>
@@ -21452,7 +21452,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H727" t="n">
         <v>14923</v>
@@ -21510,7 +21510,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H729" t="n">
         <v>4020</v>
@@ -21597,7 +21597,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H732" t="n">
         <v>8383</v>
@@ -21655,7 +21655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H734" t="n">
         <v>7575</v>
@@ -21887,7 +21887,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H742" t="n">
         <v>9642</v>
@@ -21945,7 +21945,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H744" t="n">
         <v>1128</v>
@@ -22003,7 +22003,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480491638184</v>
+        <v>1.43480479717255</v>
       </c>
       <c r="H746" t="n">
         <v>20561</v>
@@ -22061,7 +22061,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400250911713</v>
+        <v>1.44400238990784</v>
       </c>
       <c r="H748" t="n">
         <v>302</v>
@@ -22119,7 +22119,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H750" t="n">
         <v>19467</v>
@@ -22148,7 +22148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319986343384</v>
+        <v>1.45319998264313</v>
       </c>
       <c r="H751" t="n">
         <v>2586</v>
@@ -22177,7 +22177,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779860019684</v>
+        <v>1.45779871940613</v>
       </c>
       <c r="H752" t="n">
         <v>36041</v>
@@ -22206,7 +22206,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079216480255</v>
+        <v>1.48079228401184</v>
       </c>
       <c r="H753" t="n">
         <v>10446</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677953243256</v>
+        <v>1.52677965164185</v>
       </c>
       <c r="H754" t="n">
         <v>158370</v>
@@ -37002,6 +37002,35 @@
         <v>400</v>
       </c>
       <c r="I1263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1264" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1264" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="D1264" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E1264" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>1.34500002861023</v>
+      </c>
+      <c r="G1264" t="n">
+        <v>1.34500002861023</v>
+      </c>
+      <c r="H1264" t="n">
+        <v>15518</v>
+      </c>
+      <c r="I1264" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -37016,7 +37016,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="D1264" t="n">
-        <v>1.29999995231628</v>
+        <v>1.34500002861023</v>
       </c>
       <c r="E1264" t="n">
         <v>1.22500002384186</v>
@@ -37031,6 +37031,35 @@
         <v>15518</v>
       </c>
       <c r="I1264" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1265" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1265" t="n">
+        <v>1.30999994277954</v>
+      </c>
+      <c r="D1265" t="n">
+        <v>1.34500002861023</v>
+      </c>
+      <c r="E1265" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="G1265" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="H1265" t="n">
+        <v>7498</v>
+      </c>
+      <c r="I1265" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CORE.MI.xlsx
+++ b/data/CORE.MI.xlsx
@@ -456,7 +456,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33668828010559</v>
+        <v>2.33668804168701</v>
       </c>
       <c r="H3" t="n">
         <v>191052</v>
@@ -485,7 +485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22749733924866</v>
+        <v>2.22749710083008</v>
       </c>
       <c r="H4" t="n">
         <v>60317</v>
@@ -601,7 +601,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18818855285645</v>
+        <v>2.18818831443787</v>
       </c>
       <c r="H8" t="n">
         <v>38845</v>
@@ -630,7 +630,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H9" t="n">
         <v>39782</v>
@@ -659,7 +659,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H10" t="n">
         <v>12537</v>
@@ -717,7 +717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H12" t="n">
         <v>21519</v>
@@ -775,7 +775,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0440559387207</v>
+        <v>2.04405617713928</v>
       </c>
       <c r="H14" t="n">
         <v>4196</v>
@@ -833,7 +833,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H16" t="n">
         <v>212467</v>
@@ -1036,7 +1036,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G23" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H23" t="n">
         <v>9285</v>
@@ -1065,7 +1065,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G24" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H24" t="n">
         <v>3610</v>
@@ -1152,7 +1152,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G27" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H27" t="n">
         <v>18554</v>
@@ -1210,7 +1210,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H29" t="n">
         <v>7100</v>
@@ -1297,7 +1297,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G32" t="n">
-        <v>1.93486523628235</v>
+        <v>1.93486499786377</v>
       </c>
       <c r="H32" t="n">
         <v>5405</v>
@@ -1326,7 +1326,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G33" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H33" t="n">
         <v>3600</v>
@@ -1355,7 +1355,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G34" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H34" t="n">
         <v>17765</v>
@@ -1558,7 +1558,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.03532099723816</v>
+        <v>2.03532075881958</v>
       </c>
       <c r="H41" t="n">
         <v>4717</v>
@@ -1703,7 +1703,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G46" t="n">
-        <v>1.94360029697418</v>
+        <v>1.94360053539276</v>
       </c>
       <c r="H46" t="n">
         <v>21305</v>
@@ -1848,7 +1848,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G51" t="n">
-        <v>2.15761494636536</v>
+        <v>2.15761470794678</v>
       </c>
       <c r="H51" t="n">
         <v>20555</v>
@@ -2022,7 +2022,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92176222801208</v>
+        <v>1.92176246643066</v>
       </c>
       <c r="H57" t="n">
         <v>12475</v>
@@ -2080,7 +2080,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G59" t="n">
-        <v>1.88682126998901</v>
+        <v>1.88682115077972</v>
       </c>
       <c r="H59" t="n">
         <v>31353</v>
@@ -2109,7 +2109,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>1.89555644989014</v>
+        <v>1.89555656909943</v>
       </c>
       <c r="H60" t="n">
         <v>26975</v>
@@ -2138,7 +2138,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G61" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H61" t="n">
         <v>15420</v>
@@ -2167,7 +2167,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G62" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2225,7 +2225,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G64" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H64" t="n">
         <v>27250</v>
@@ -2312,7 +2312,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07026195526123</v>
+        <v>2.07026219367981</v>
       </c>
       <c r="H67" t="n">
         <v>164735</v>
@@ -2370,7 +2370,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G69" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H69" t="n">
         <v>10560</v>
@@ -2399,7 +2399,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G70" t="n">
-        <v>2.09646821022034</v>
+        <v>2.09646797180176</v>
       </c>
       <c r="H70" t="n">
         <v>2080</v>
@@ -2544,7 +2544,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G75" t="n">
-        <v>2.09210014343262</v>
+        <v>2.0921003818512</v>
       </c>
       <c r="H75" t="n">
         <v>24848</v>
@@ -2689,7 +2689,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>2.11393857002258</v>
+        <v>2.11393880844116</v>
       </c>
       <c r="H80" t="n">
         <v>3341</v>
@@ -2863,7 +2863,7 @@
         <v>2.14499998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>1.87371814250946</v>
+        <v>1.87371826171875</v>
       </c>
       <c r="H86" t="n">
         <v>7811</v>
@@ -3269,7 +3269,7 @@
         <v>2.10500001907349</v>
       </c>
       <c r="G100" t="n">
-        <v>1.8387770652771</v>
+        <v>1.83877718448639</v>
       </c>
       <c r="H100" t="n">
         <v>42528</v>
@@ -3385,7 +3385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G104" t="n">
-        <v>1.93923282623291</v>
+        <v>1.93923306465149</v>
       </c>
       <c r="H104" t="n">
         <v>63970</v>
@@ -3559,7 +3559,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G110" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H110" t="n">
         <v>3088</v>
@@ -3907,7 +3907,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H122" t="n">
         <v>16909</v>
@@ -3994,7 +3994,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>1.86061537265778</v>
+        <v>1.86061549186707</v>
       </c>
       <c r="H125" t="n">
         <v>101033</v>
@@ -4023,7 +4023,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G126" t="n">
-        <v>1.91302692890167</v>
+        <v>1.91302716732025</v>
       </c>
       <c r="H126" t="n">
         <v>17450</v>
@@ -4052,7 +4052,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G127" t="n">
-        <v>1.85188007354736</v>
+        <v>1.85187995433807</v>
       </c>
       <c r="H127" t="n">
         <v>13630</v>
@@ -4168,7 +4168,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H131" t="n">
         <v>7054</v>
@@ -4255,7 +4255,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G134" t="n">
-        <v>1.84314477443695</v>
+        <v>1.84314453601837</v>
       </c>
       <c r="H134" t="n">
         <v>16500</v>
@@ -4342,7 +4342,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G137" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H137" t="n">
         <v>1563</v>
@@ -4632,7 +4632,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G147" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H147" t="n">
         <v>3822</v>
@@ -4806,7 +4806,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G153" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H153" t="n">
         <v>138668</v>
@@ -4835,7 +4835,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G154" t="n">
-        <v>1.55488038063049</v>
+        <v>1.5548802614212</v>
       </c>
       <c r="H154" t="n">
         <v>63112</v>
@@ -4893,7 +4893,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G156" t="n">
-        <v>1.6247626543045</v>
+        <v>1.62476277351379</v>
       </c>
       <c r="H156" t="n">
         <v>7318</v>
@@ -4922,7 +4922,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G157" t="n">
-        <v>1.57235085964203</v>
+        <v>1.57235097885132</v>
       </c>
       <c r="H157" t="n">
         <v>46024</v>
@@ -5038,7 +5038,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G161" t="n">
-        <v>1.58108627796173</v>
+        <v>1.58108615875244</v>
       </c>
       <c r="H161" t="n">
         <v>13350</v>
@@ -5154,7 +5154,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G165" t="n">
-        <v>1.61602747440338</v>
+        <v>1.61602735519409</v>
       </c>
       <c r="H165" t="n">
         <v>10225</v>
@@ -5212,7 +5212,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G167" t="n">
-        <v>1.66843903064728</v>
+        <v>1.66843891143799</v>
       </c>
       <c r="H167" t="n">
         <v>51514</v>
@@ -5444,7 +5444,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G175" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H175" t="n">
         <v>5050</v>
@@ -5531,7 +5531,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G178" t="n">
-        <v>1.816938996315</v>
+        <v>1.81693875789642</v>
       </c>
       <c r="H178" t="n">
         <v>14700</v>
@@ -5589,7 +5589,7 @@
         <v>2.01500010490417</v>
       </c>
       <c r="G180" t="n">
-        <v>1.76015961170197</v>
+        <v>1.76015973091125</v>
       </c>
       <c r="H180" t="n">
         <v>15133</v>
@@ -5676,7 +5676,7 @@
         <v>2.04500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>1.78636562824249</v>
+        <v>1.7863655090332</v>
       </c>
       <c r="H183" t="n">
         <v>8218</v>
@@ -17421,7 +17421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G588" t="n">
-        <v>1.71992635726929</v>
+        <v>1.71992647647858</v>
       </c>
       <c r="H588" t="n">
         <v>9100</v>
@@ -17450,7 +17450,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G589" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H589" t="n">
         <v>18340</v>
@@ -17479,7 +17479,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G590" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H590" t="n">
         <v>10566</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.73832142353058</v>
+        <v>1.73832130432129</v>
       </c>
       <c r="H592" t="n">
         <v>4380</v>
@@ -17566,7 +17566,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G593" t="n">
-        <v>1.71072888374329</v>
+        <v>1.71072900295258</v>
       </c>
       <c r="H593" t="n">
         <v>3000</v>
@@ -17595,7 +17595,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G594" t="n">
-        <v>1.70153152942657</v>
+        <v>1.70153141021729</v>
       </c>
       <c r="H594" t="n">
         <v>7533</v>
@@ -17653,7 +17653,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G596" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H596" t="n">
         <v>15693</v>
@@ -17740,7 +17740,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G599" t="n">
-        <v>1.65554404258728</v>
+        <v>1.65554416179657</v>
       </c>
       <c r="H599" t="n">
         <v>4008</v>
@@ -17769,7 +17769,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G600" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H600" t="n">
         <v>3000</v>
@@ -17798,7 +17798,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G601" t="n">
-        <v>1.64174783229828</v>
+        <v>1.64174795150757</v>
       </c>
       <c r="H601" t="n">
         <v>9280</v>
@@ -17827,7 +17827,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G602" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H602" t="n">
         <v>17225</v>
@@ -17914,7 +17914,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G605" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H605" t="n">
         <v>16118</v>
@@ -18030,7 +18030,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G609" t="n">
-        <v>1.59576070308685</v>
+        <v>1.59576058387756</v>
       </c>
       <c r="H609" t="n">
         <v>91019</v>
@@ -18088,7 +18088,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G611" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H611" t="n">
         <v>98468</v>
@@ -18117,7 +18117,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G612" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H612" t="n">
         <v>22288</v>
@@ -18146,7 +18146,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G613" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H613" t="n">
         <v>43946</v>
@@ -18175,7 +18175,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G614" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H614" t="n">
         <v>28101</v>
@@ -18204,7 +18204,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G615" t="n">
-        <v>1.50838458538055</v>
+        <v>1.50838470458984</v>
       </c>
       <c r="H615" t="n">
         <v>25297</v>
@@ -18233,7 +18233,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G616" t="n">
-        <v>1.49918711185455</v>
+        <v>1.49918723106384</v>
       </c>
       <c r="H616" t="n">
         <v>968</v>
@@ -18262,7 +18262,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G617" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H617" t="n">
         <v>150</v>
@@ -18320,7 +18320,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G619" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H619" t="n">
         <v>1200</v>
@@ -18407,7 +18407,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G622" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H622" t="n">
         <v>12894</v>
@@ -18436,7 +18436,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G623" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H623" t="n">
         <v>20448</v>
@@ -18494,7 +18494,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G625" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H625" t="n">
         <v>1672</v>
@@ -18610,7 +18610,7 @@
         <v>1.50499999523163</v>
       </c>
       <c r="G629" t="n">
-        <v>1.38421893119812</v>
+        <v>1.38421881198883</v>
       </c>
       <c r="H629" t="n">
         <v>2550</v>
@@ -18639,7 +18639,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G630" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H630" t="n">
         <v>20080</v>
@@ -18697,7 +18697,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G632" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H632" t="n">
         <v>4000</v>
@@ -18813,7 +18813,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G636" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H636" t="n">
         <v>23082</v>
@@ -18842,7 +18842,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G637" t="n">
-        <v>1.57736563682556</v>
+        <v>1.57736575603485</v>
       </c>
       <c r="H637" t="n">
         <v>26688</v>
@@ -18929,7 +18929,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G640" t="n">
-        <v>1.63714921474457</v>
+        <v>1.63714909553528</v>
       </c>
       <c r="H640" t="n">
         <v>4804</v>
@@ -18958,7 +18958,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G641" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H641" t="n">
         <v>41120</v>
@@ -19016,7 +19016,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G643" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H643" t="n">
         <v>15100</v>
@@ -19074,7 +19074,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G645" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H645" t="n">
         <v>111562</v>
@@ -19103,7 +19103,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G646" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H646" t="n">
         <v>16300</v>
@@ -19161,7 +19161,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H648" t="n">
         <v>4602</v>
@@ -19190,7 +19190,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G649" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H649" t="n">
         <v>30369</v>
@@ -19277,7 +19277,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G652" t="n">
-        <v>1.55897080898285</v>
+        <v>1.55897068977356</v>
       </c>
       <c r="H652" t="n">
         <v>100565</v>
@@ -19741,7 +19741,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H668" t="n">
         <v>200</v>
@@ -20060,7 +20060,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G679" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H679" t="n">
         <v>31887</v>
@@ -20089,7 +20089,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G680" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H680" t="n">
         <v>27161</v>
@@ -20176,7 +20176,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G683" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H683" t="n">
         <v>3002</v>
@@ -20205,7 +20205,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G684" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H684" t="n">
         <v>0</v>
@@ -20263,7 +20263,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G686" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H686" t="n">
         <v>1802</v>
@@ -20292,7 +20292,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G687" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H687" t="n">
         <v>10888</v>
@@ -20408,7 +20408,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G691" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H691" t="n">
         <v>9583</v>
@@ -20553,7 +20553,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G696" t="n">
-        <v>1.36582386493683</v>
+        <v>1.36582398414612</v>
       </c>
       <c r="H696" t="n">
         <v>32055</v>
@@ -20698,7 +20698,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.35662639141083</v>
+        <v>1.35662651062012</v>
       </c>
       <c r="H701" t="n">
         <v>11820</v>
@@ -20727,7 +20727,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G702" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H702" t="n">
         <v>1998</v>
@@ -20756,7 +20756,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G703" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H703" t="n">
         <v>350</v>
@@ -20785,7 +20785,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G704" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H704" t="n">
         <v>0</v>
@@ -20814,7 +20814,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G705" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H705" t="n">
         <v>0</v>
@@ -20843,7 +20843,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G706" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H706" t="n">
         <v>0</v>
@@ -20872,7 +20872,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G707" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H707" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G710" t="n">
-        <v>1.38881766796112</v>
+        <v>1.38881754875183</v>
       </c>
       <c r="H710" t="n">
         <v>1020</v>
@@ -21075,7 +21075,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G714" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H714" t="n">
         <v>10966</v>
@@ -21104,7 +21104,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G715" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H715" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G717" t="n">
-        <v>1.42560744285583</v>
+        <v>1.42560732364655</v>
       </c>
       <c r="H717" t="n">
         <v>27660</v>
@@ -21249,7 +21249,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G720" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H720" t="n">
         <v>2970</v>
@@ -21278,7 +21278,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H721" t="n">
         <v>1755</v>
@@ -21307,7 +21307,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H722" t="n">
         <v>1321</v>
@@ -21336,7 +21336,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G723" t="n">
-        <v>1.43020606040955</v>
+        <v>1.43020617961884</v>
       </c>
       <c r="H723" t="n">
         <v>4341</v>
@@ -21423,7 +21423,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G726" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H726" t="n">
         <v>6092</v>
@@ -21452,7 +21452,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G727" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H727" t="n">
         <v>14923</v>
@@ -21510,7 +21510,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G729" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H729" t="n">
         <v>4020</v>
@@ -21597,7 +21597,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G732" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H732" t="n">
         <v>8383</v>
@@ -21655,7 +21655,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G734" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H734" t="n">
         <v>7575</v>
@@ -21887,7 +21887,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G742" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H742" t="n">
         <v>9642</v>
@@ -21945,7 +21945,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G744" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H744" t="n">
         <v>1128</v>
@@ -22003,7 +22003,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G746" t="n">
-        <v>1.43480479717255</v>
+        <v>1.43480491638184</v>
       </c>
       <c r="H746" t="n">
         <v>20561</v>
@@ -22061,7 +22061,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G748" t="n">
-        <v>1.44400238990784</v>
+        <v>1.44400250911713</v>
       </c>
       <c r="H748" t="n">
         <v>302</v>
@@ -22119,7 +22119,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G750" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H750" t="n">
         <v>19467</v>
@@ -22148,7 +22148,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G751" t="n">
-        <v>1.45319998264313</v>
+        <v>1.45319986343384</v>
       </c>
       <c r="H751" t="n">
         <v>2586</v>
@@ -22177,7 +22177,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.45779871940613</v>
+        <v>1.45779860019684</v>
       </c>
       <c r="H752" t="n">
         <v>36041</v>
@@ -22206,7 +22206,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G753" t="n">
-        <v>1.48079228401184</v>
+        <v>1.48079216480255</v>
       </c>
       <c r="H753" t="n">
         <v>10446</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.52677965164185</v>
+        <v>1.52677953243256</v>
       </c>
       <c r="H754" t="n">
         <v>158370</v>
@@ -37060,6 +37060,35 @@
         <v>7498</v>
       </c>
       <c r="I1265" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1266" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1266" t="n">
+        <v>1.26499998569489</v>
+      </c>
+      <c r="D1266" t="n">
+        <v>1.29999995231628</v>
+      </c>
+      <c r="E1266" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="G1266" t="n">
+        <v>1.25999999046326</v>
+      </c>
+      <c r="H1266" t="n">
+        <v>12016</v>
+      </c>
+      <c r="I1266" t="s">
         <v>9</v>
       </c>
     </row>
